--- a/workspaces/btc_daily_14days/dxy/dxy_ret_10.xlsx
+++ b/workspaces/btc_daily_14days/dxy/dxy_ret_10.xlsx
@@ -575,46 +575,46 @@
         <v>20</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.482862869248386</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-4.108046075625616</v>
+        <v>-4.092875363367554</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-4.502955508968057</v>
+        <v>-4.487581162988704</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.6305903809183704</v>
+        <v>0.6295009405076328</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.09139535770458451</v>
+        <v>0.09417495800476416</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.3893769039695201</v>
+        <v>0.3894176827469948</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.3046431866972412</v>
+        <v>0.304683965474716</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>19.86308517123717</v>
+        <v>19.7990624917125</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>4.787623051400239</v>
+        <v>4.769044987806268</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>8.942979415904958</v>
+        <v>8.915265436422871</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>8.737736120680509</v>
+        <v>8.710838759377864</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>8.77987296899849</v>
+        <v>8.750007834304398</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>3.349398698556129</v>
+        <v>3.335726250299111</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>8.61194306800644</v>
+        <v>8.585447582575398</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>10</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.48265791864867</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-14.11456903895833</v>
+        <v>-14.06678351004353</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-34.52240751030752</v>
+        <v>-34.40977315761836</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-34.39202982810314</v>
+        <v>-34.28001822340291</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-34.93123985729341</v>
+        <v>-34.81528418200497</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-34.65590154968251</v>
+        <v>-34.54266463677752</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-4.701825435130807</v>
+        <v>-4.685613101784632</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-5.168759413398625</v>
+        <v>-5.15317063133552</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>4.787839494859867</v>
+        <v>4.768900692167655</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-16.10524139209913</v>
+        <v>-16.05258735823993</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-6.291076725597392</v>
+        <v>-6.269952676439331</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-6.25852290973566</v>
+        <v>-6.240393196009641</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-16.71514428689738</v>
+        <v>-16.66427374970203</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-6.436148400196771</v>
+        <v>-6.414552417424602</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>14</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-9.636295463067121</v>
+        <v>-9.602064595173701</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-4.108195503756647</v>
+        <v>-4.092277650840494</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>9.791842371879525</v>
+        <v>9.761798742203268</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-4.372811077745737</v>
+        <v>-4.356893224829584</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>2.23548308458642</v>
+        <v>2.232109764763379</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-4.617446637386273</v>
+        <v>-4.600347005218552</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-11.85410904840912</v>
+        <v>-11.81433053901026</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-19.47322114094038</v>
+        <v>-19.41076375430876</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-5.231577409935106</v>
+        <v>-5.218154704636724</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-13.2429951969542</v>
+        <v>-13.19884672643217</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-20.60498260449349</v>
+        <v>-20.53687256669502</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-20.58181297822708</v>
+        <v>-20.51671353603188</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-6.683241666157848</v>
+        <v>-6.664273749700079</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-6.436487382267032</v>
+        <v>-6.414552417425412</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>21</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.1124859392575885</v>
+        <v>-0.1089364773417643</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>12.56942039683528</v>
+        <v>12.53059208011995</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-6.88570813160009</v>
+        <v>-6.861332577217823</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-1.99035768660243</v>
+        <v>-1.981944884647135</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-7.294609637824919</v>
+        <v>-7.266566964641861</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-2.233501198915519</v>
+        <v>-2.223884210544533</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>7.218353373772516</v>
+        <v>7.196023446765444</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-7.553280466889213</v>
+        <v>-7.528770003483046</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-7.617446833241011</v>
+        <v>-7.59582905735261</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-13.24360918230469</v>
+        <v>-13.19843740286463</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-3.906150580737524</v>
+        <v>-3.891649471423925</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-13.42122976234696</v>
+        <v>-13.37828791142913</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-9.072528688346011</v>
+        <v>-9.045226130653276</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-8.825843268308766</v>
+        <v>-8.795504798376989</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>24</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-6.660104986876647</v>
+        <v>-6.634461622324849</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-4.108212137987202</v>
+        <v>-4.092211113921408</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-8.672769926906994</v>
+        <v>-8.641656824557103</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-4.372961053842907</v>
+        <v>-4.356293320442617</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.7427599215295331</v>
+        <v>-0.7358705917236321</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.4455015582717863</v>
+        <v>-0.4415979572268895</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.5298792226218083</v>
+        <v>-0.5268657538801875</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>7.347389947971685</v>
+        <v>7.322605326609157</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>7.293155061301071</v>
+        <v>7.265356981207049</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>2.263004533039883</v>
+        <v>2.257470913889549</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>6.233062322902768</v>
+        <v>6.213954624562454</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>2.095606407628857</v>
+        <v>2.087741141313991</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>1.677028463592144</v>
+        <v>1.66905958363197</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>1.923621824296127</v>
+        <v>1.918780915909203</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>28</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-6.064866891638545</v>
+        <v>-6.040347918270996</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-4.108326117884822</v>
+        <v>-4.09175519433186</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-4.50347100654043</v>
+        <v>-4.485519172691994</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-7.94695453828519</v>
+        <v>-7.917462239818697</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-4.912329544153238</v>
+        <v>-4.890925434564096</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-1.04161125809604</v>
+        <v>-1.035528645583881</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>6.026672352718556</v>
+        <v>6.007354502155373</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.593067445461635</v>
+        <v>-1.588137154669731</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.653193057385572</v>
+        <v>-1.651363320622799</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-2.508579971916291</v>
+        <v>-2.497980685981659</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-13.44980333246394</v>
+        <v>-13.40223017662151</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-6.260380417986219</v>
+        <v>-6.239928818948428</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-10.26833057562394</v>
+        <v>-10.23570232112905</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-2.854462742948229</v>
+        <v>-2.843123845996033</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>43</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>7.971677958859786</v>
+        <v>7.947930446230586</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1.709564312176724</v>
+        <v>1.706450527282421</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1.314405585182037</v>
+        <v>1.312741902277949</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.444755391255569</v>
+        <v>1.44260834102159</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>7.887180239875605</v>
+        <v>7.864523801411579</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>10.51942353035702</v>
+        <v>10.48504541758405</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>8.10640454652161</v>
+        <v>8.07878611178409</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>9.967990454528341</v>
+        <v>9.932402241191546</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>9.91607906972326</v>
+        <v>9.87720609187091</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>9.060428139082987</v>
+        <v>9.030764737250948</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>4.194069244110274</v>
+        <v>4.181810475539777</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>6.565678741490927</v>
+        <v>6.541928484205805</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>1.482433453627642</v>
+        <v>1.475261134020045</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>6.396859639469668</v>
+        <v>6.37614525699427</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>54</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>4.91396908719743</v>
+        <v>4.899741395413976</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-7.815031434385624</v>
+        <v>-7.783452446847406</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.7973687587940645</v>
+        <v>-0.7914096451593196</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-6.226643604556216</v>
+        <v>-6.200822376853118</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1.206158161553915</v>
+        <v>-1.197092446443072</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.9456401216858694</v>
+        <v>0.943911745060511</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>6.425138410630353</v>
+        <v>6.401718907351984</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.3942415186201202</v>
+        <v>0.3912168595250023</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.3359435325639666</v>
+        <v>0.3294239262902394</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>5.047700229001741</v>
+        <v>5.030636746210469</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>6.697946053192958</v>
+        <v>6.675637075974223</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>6.739805854387498</v>
+        <v>6.713728316661737</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>8.182784845102027</v>
+        <v>8.15054106511392</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.9952418108431402</v>
+        <v>0.9928549899825967</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>65</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>7.506561679790025</v>
+        <v>7.481051418118035</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>4.359003999163043</v>
+        <v>4.346616645168808</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>7.043315833228938</v>
+        <v>7.019641160537283</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>7.173512442283901</v>
+        <v>7.150120387356374</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>8.174116262015218</v>
+        <v>8.147906725378604</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>5.397001420113781</v>
+        <v>5.377980908529757</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>6.854007318482516</v>
+        <v>6.826791613949894</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>7.927318144702546</v>
+        <v>7.895020723819506</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>9.417103600932371</v>
+        <v>9.375032313759469</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>11.64507113304954</v>
+        <v>11.60105044550696</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>8.355421815129091</v>
+        <v>8.324689322052663</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>5.312821476908212</v>
+        <v>5.289847630404843</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>1.807924742252496</v>
+        <v>1.797264711837578</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>8.231290052608983</v>
+        <v>8.200832197960011</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>88</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>3.188379861608333</v>
+        <v>3.177475577685847</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.6973058628053082</v>
+        <v>-0.6903816691952613</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.182430990327639</v>
+        <v>1.179963748926234</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.449923232054104</v>
+        <v>2.4430786268763</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.910865309523182</v>
+        <v>1.907204241637508</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>4.487369463455074</v>
+        <v>4.469701570790221</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>4.403783651924677</v>
+        <v>4.383245994905629</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>3.936345162978299</v>
+        <v>3.916445231371512</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>9.57803414911475</v>
+        <v>9.529983043875596</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>9.860771112056739</v>
+        <v>9.818555820807291</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>13.07223361599961</v>
+        <v>13.01814345946751</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>15.40091259938193</v>
+        <v>15.33338429034599</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>11.56985652161604</v>
+        <v>11.51754443211728</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>12.95744881243382</v>
+        <v>12.90362940075723</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>80</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-2.493438320210259</v>
+        <v>-2.480843779012787</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-4.109619554032882</v>
+        <v>-4.086581449739768</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-7.006554376331962</v>
+        <v>-6.973185693526261</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-6.876301243724463</v>
+        <v>-6.842932560918761</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-6.16434763249643</v>
+        <v>-6.13285308119103</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-8.37523540760867</v>
+        <v>-8.338663849886501</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-7.206436056903321</v>
+        <v>-7.178697169125506</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-5.169483806387809</v>
+        <v>-5.152084041852454</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-10.24298623567801</v>
+        <v>-10.21054882080789</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-6.086858778744485</v>
+        <v>-6.064842433810171</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-7.545817224944344</v>
+        <v>-7.516792343539279</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-6.258574869192557</v>
+        <v>-6.240380206146881</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-4.173791731137776</v>
+        <v>-4.164273749701032</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-5.182934824512955</v>
+        <v>-5.164552417424609</v>
       </c>
     </row>
     <row r="17">
@@ -1144,49 +1144,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>4.028300810224934</v>
+        <v>4.052936395798454</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-6.286390423938045</v>
+        <v>-6.341437842934006</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-6.681259130534634</v>
+        <v>-6.736306549530596</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-5.46300231190888</v>
+        <v>-5.510328332758547</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-2.738179771601409</v>
+        <v>-2.767999401256041</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-2.442323614934956</v>
+        <v>-2.463079908245334</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.830862420476386</v>
+        <v>1.847319587072114</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.2746261517942159</v>
+        <v>0.2833544743439163</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.386414945251481</v>
+        <v>-1.379316467918436</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>3.230970041469497</v>
+        <v>3.259254321808157</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.2369694242918783</v>
+        <v>-0.2349892505956035</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.8768181349978192</v>
+        <v>0.8961829215881565</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.811428343176658</v>
+        <v>-2.818119903546922</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.55544871702871</v>
+        <v>-2.568398571270755</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>84</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>7.030371203599614</v>
+        <v>7.001969999883826</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1.847044426505661</v>
+        <v>1.848342797310174</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.260451650826603</v>
+        <v>0.2667415360564718</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.3908057678299173</v>
+        <v>0.3966917154761589</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.339945422700218</v>
+        <v>-1.326644335127149</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.042914935619834</v>
+        <v>-1.035441490562548</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.124815393257201</v>
+        <v>-1.123008467469745</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.785175734258637</v>
+        <v>-2.777967304983683</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-6.422266060401384</v>
+        <v>-6.405733894062756</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>2.266750645995899</v>
+        <v>2.252618077102966</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>2.060378316172823</v>
+        <v>2.049483758291146</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-2.674415621673369</v>
+        <v>-2.671982215878813</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-3.098345907953473</v>
+        <v>-3.09284517827232</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-2.852688439293928</v>
+        <v>-2.843123845995898</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>99</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>3.062117235345461</v>
+        <v>3.046187521808484</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>2.46096784697297</v>
+        <v>2.459674989010082</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2.065976541776386</v>
+        <v>2.065174078213346</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.8374949713896314</v>
+        <v>-0.8246109730703708</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>3.679637697294581</v>
+        <v>3.672326362608345</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.957524575898098</v>
+        <v>1.952574986375254</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.876231245325236</v>
+        <v>1.864400882403451</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-2.64130998221875</v>
+        <v>-2.633232768423532</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-5.737006466134034</v>
+        <v>-5.720142117478801</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.540951434820158</v>
+        <v>-2.535639438040391</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.7227375219205072</v>
+        <v>-0.722955959171216</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>3.370912129854226</v>
+        <v>3.345616566320025</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>5.997817610128905</v>
+        <v>5.961988876561797</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.876143940241569</v>
+        <v>-1.869097871970119</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>84</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.077990251218594</v>
+        <v>1.068564903431998</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.729087253337916</v>
+        <v>-1.70897644887318</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-9.276229206821725</v>
+        <v>-9.218453986236817</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2.77392311170987</v>
+        <v>2.771149207645742</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.340862273623664</v>
+        <v>-1.323893782356613</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.343244204460049</v>
+        <v>1.340304131262329</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-7.092209830745695</v>
+        <v>-7.06037593474322</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-6.367649766120934</v>
+        <v>-6.338350415978468</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-7.619784824703103</v>
+        <v>-7.589167510713409</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-6.086118937415293</v>
+        <v>-6.06117900615218</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-12.26053881687972</v>
+        <v>-12.20102768008529</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-13.42869086919824</v>
+        <v>-13.37293808575143</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-13.86572900903461</v>
+        <v>-13.8071308925581</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-7.64362826137728</v>
+        <v>-7.605028607900863</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>103</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-2.978875213413801</v>
+        <v>-2.96667885444058</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.260460966743878</v>
+        <v>0.2742975224111461</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.808887491301107</v>
+        <v>1.816533413615389</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.9762876333240484</v>
+        <v>-0.9574141189723875</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.4289747111591495</v>
+        <v>0.4401042785514022</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.218325494828086</v>
+        <v>-1.206771569357365</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-4.221688158880205</v>
+        <v>-4.198119058296186</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-3.717033683886505</v>
+        <v>-3.695392758037528</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-4.749092612480531</v>
+        <v>-4.727081174623585</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-5.6027225386444</v>
+        <v>-5.573701618515678</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-7.759329339829527</v>
+        <v>-7.710096611596505</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-9.678764247848029</v>
+        <v>-9.629848438961574</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-8.161455721620989</v>
+        <v>-8.120584429312537</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-8.898629722337368</v>
+        <v>-8.841736883444021</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>98</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.4526219936793083</v>
+        <v>-0.4538293907923858</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.9936360983673893</v>
+        <v>1.007207237506933</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>3.664049287699683</v>
+        <v>3.661390802307402</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.773417230429139</v>
+        <v>2.772666851487806</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.212009764443124</v>
+        <v>1.221571736096024</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2.537595413652959</v>
+        <v>2.526905303021664</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-2.665004570442775</v>
+        <v>-2.644043780080104</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-6.206280383940175</v>
+        <v>-6.159583743737599</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.168139065644958</v>
+        <v>-2.156459528275086</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-4.047001881427072</v>
+        <v>-4.018663409079323</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.186621404867829</v>
+        <v>-1.166101554681944</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-3.198348072461179</v>
+        <v>-3.177610174459637</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.571325960727364</v>
+        <v>-1.562232933374368</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.74636385663166</v>
+        <v>1.748712888697845</v>
       </c>
     </row>
     <row r="23">
@@ -1456,49 +1456,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-2.493438320210061</v>
+        <v>-2.500612518015835</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>2.014797275076418</v>
+        <v>2.009925944457123</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>7.754605454399147</v>
+        <v>7.772299023085331</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>2.773495129937906</v>
+        <v>2.773985062615125</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.21101710213167</v>
+        <v>1.204773960016148</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-6.682850276747239</v>
+        <v>-6.711847506952068</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-2.669365838926019</v>
+        <v>-2.683059951276178</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.092290924529117</v>
+        <v>-1.10280918321984</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-2.170569202932015</v>
+        <v>-2.178199683184587</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-4.052898209006848</v>
+        <v>-4.071412311645538</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-7.339337567638665</v>
+        <v>-7.37673113661144</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-4.667815633221679</v>
+        <v>-4.687080267804014</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-5.098189024692978</v>
+        <v>-5.117881997123575</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-6.89477107248765</v>
+        <v>-6.930016334950373</v>
       </c>
     </row>
     <row r="24">
@@ -1508,49 +1508,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>4.173228346456725</v>
+        <v>4.199710556210057</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>4.787180019182777</v>
+        <v>4.794713972935938</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.052470451226156</v>
+        <v>1.045161391614947</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>3.410208522850212</v>
+        <v>3.414903188062056</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>2.869014213448452</v>
+        <v>2.867383730919734</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>3.171777636111216</v>
+        <v>3.177031279365231</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.973443734573266</v>
+        <v>1.975858715746469</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>4.851518930059775</v>
+        <v>4.867534068366446</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.901112655026395</v>
+        <v>-1.913568873709359</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.5296100233615135</v>
+        <v>-0.5427441314965833</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>4.835866594384918</v>
+        <v>4.83946788209942</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>2.651965466140744</v>
+        <v>2.660057771475621</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>3.992036941959121</v>
+        <v>4.009883553669901</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>7.608964146550974</v>
+        <v>7.630391402800115</v>
       </c>
     </row>
     <row r="25">
@@ -1560,49 +1560,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-6.243438320209975</v>
+        <v>-6.289319610424485</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>10.92038593791205</v>
+        <v>10.99207866262403</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>6.763966834311248</v>
+        <v>6.803055273808582</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>5.640947715609819</v>
+        <v>5.670799293817481</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3.844053319996057</v>
+        <v>3.849986932877535</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>7.365490884562888</v>
+        <v>7.414709671176368</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>1.005216589167567</v>
+        <v>1.000862029853458</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1.797017477118381</v>
+        <v>1.799501415882091</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>4.237027915804468</v>
+        <v>4.270147099320035</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>7.171123411800671</v>
+        <v>7.217490268722493</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>6.985750943021756</v>
+        <v>7.012736944404871</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>4.482784671363788</v>
+        <v>4.515474532130092</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>2.805968380628833</v>
+        <v>2.829397136375057</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>5.588193928023941</v>
+        <v>5.610764038271597</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>65</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>4.429638602866966</v>
+        <v>4.41095024405049</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>5.914827673386867</v>
+        <v>5.894988066825789</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.662647093425079</v>
+        <v>-0.6537267936169755</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>5.647417788614447</v>
+        <v>5.630372492836678</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>6.645566578550543</v>
+        <v>6.630412816226006</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>6.954185759399259</v>
+        <v>6.927854753941709</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>5.320307638594038</v>
+        <v>5.30465949820789</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>7.941632959137003</v>
+        <v>7.914399176349463</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>4.797712975196781</v>
+        <v>4.776476213244088</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>3.939204857819036</v>
+        <v>3.92635102821616</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>6.813180165084582</v>
+        <v>6.798520780821654</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>5.316581938988179</v>
+        <v>5.294442399705552</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>4.896327328043277</v>
+        <v>4.874187788760651</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>6.679824354544593</v>
+        <v>6.662370659498428</v>
       </c>
     </row>
     <row r="27">
@@ -1664,49 +1664,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-12.10882293559462</v>
+        <v>-12.32207565749785</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-8.835618878971097</v>
+        <v>-9.006972717488011</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-5.335648247690344</v>
+        <v>-5.480272796633599</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.5313786596656058</v>
+        <v>0.532333277150407</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.03352868769638206</v>
+        <v>-0.006087937921705588</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-1.657020286629518</v>
+        <v>-1.669430313931571</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>7.906087605965141</v>
+        <v>8.049757537423609</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>3.584636112409193</v>
+        <v>3.661005511191121</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1.576216557288227</v>
+        <v>1.639221311283301</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.148300059093145</v>
+        <v>-1.171688187470146</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.6187090313896633</v>
+        <v>0.5843428019377939</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.34301297192706</v>
+        <v>-1.342058354442258</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.763267582871961</v>
+        <v>-1.76231296538716</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>4.312484258979175</v>
+        <v>4.369761308065648</v>
       </c>
     </row>
     <row r="28">
@@ -2213,10 +2213,8 @@
           <t>X &gt; -0.02379</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>1573~1578</t>
-        </is>
+      <c r="B6" t="n">
+        <v>1573</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>0.8018721994351452</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; -0.02212</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>1553~1558</t>
-        </is>
+      <c r="B7" t="n">
+        <v>1553</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>0.8441740032816796</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; -0.02046</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>1543~1548</t>
-        </is>
+      <c r="B8" t="n">
+        <v>1543</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>0.8657348064050154</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; -0.01879</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>1529~1534</t>
-        </is>
+      <c r="B9" t="n">
+        <v>1529</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>0.9615812365044931</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; -0.01713</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>1508~1513</t>
-        </is>
+      <c r="B10" t="n">
+        <v>1508</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>0.9764889765514226</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; -0.01546</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1484~1489</t>
-        </is>
+      <c r="B11" t="n">
+        <v>1484</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>1.099577126398486</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; -0.01379</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1456~1461</t>
-        </is>
+      <c r="B12" t="n">
+        <v>1456</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>1.236883377257513</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; -0.01213</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1413~1418</t>
-        </is>
+      <c r="B13" t="n">
+        <v>1413</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>1.032654768647568</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; -0.01046</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1359~1364</t>
-        </is>
+      <c r="B14" t="n">
+        <v>1359</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>0.8789956973853279</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; -0.008795</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1294~1299</t>
-        </is>
+      <c r="B15" t="n">
+        <v>1294</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>0.5473622956483766</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; -0.007129</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1206~1211</t>
-        </is>
+      <c r="B16" t="n">
+        <v>1206</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>0.3554468986174371</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; -0.005462</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1126~1131</t>
-        </is>
+      <c r="B17" t="n">
+        <v>1126</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>0.556959557774114</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; -0.003796</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1035~1039</t>
-        </is>
+      <c r="B18" t="n">
+        <v>1035</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>0.2495838164598965</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; -0.00213</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>951~955</t>
-        </is>
+      <c r="B19" t="n">
+        <v>951</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-0.3468414615712376</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; -0.0004641</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>852~856</t>
-        </is>
+      <c r="B20" t="n">
+        <v>852</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-0.7411018716118392</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; 0.001202</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>768~772</t>
-        </is>
+      <c r="B21" t="n">
+        <v>768</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-0.9390341751322495</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; 0.002868</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>665~669</t>
-        </is>
+      <c r="B22" t="n">
+        <v>665</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-0.6249779315702142</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; 0.004534</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>567~571</t>
-        </is>
+      <c r="B23" t="n">
+        <v>567</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-0.6545591608404564</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 0.0062</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>470~473</t>
-        </is>
+      <c r="B24" t="n">
+        <v>470</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-0.2735651701042627</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 0.007867</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>381~383</t>
-        </is>
+      <c r="B25" t="n">
+        <v>381</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-1.31850359436141</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 0.009533</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>302~303</t>
-        </is>
+      <c r="B26" t="n">
+        <v>302</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-0.01819079545749958</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 0.0112</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>237~238</t>
-        </is>
+      <c r="B27" t="n">
+        <v>237</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-1.232934118529307</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 0.01286</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>186~186</t>
-        </is>
+      <c r="B28" t="n">
+        <v>186</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>1.807636948607225</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 0.01453</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>136~136</t>
-        </is>
+      <c r="B29" t="n">
+        <v>136</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-1.758144202562917</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 0.0162</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>105~105</t>
-        </is>
+      <c r="B30" t="n">
+        <v>105</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-2.96962879640045</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 0.01786</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>86~86</t>
-        </is>
+      <c r="B31" t="n">
+        <v>86</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-2.493438320209975</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 0.01953</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>68~68</t>
-        </is>
+      <c r="B32" t="n">
+        <v>68</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-5.434614790798214</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 0.0212</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>55~55</t>
-        </is>
+      <c r="B33" t="n">
+        <v>55</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-1.584347411119069</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 0.02286</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>44~44</t>
-        </is>
+      <c r="B34" t="n">
+        <v>44</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-4.766165592937249</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 0.02453</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>33~33</t>
-        </is>
+      <c r="B35" t="n">
+        <v>33</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-0.9782868050584597</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; -0.02379</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>33~33</t>
-        </is>
+      <c r="B6" t="n">
+        <v>33</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>5.082319255547603</v>
@@ -4021,10 +3959,8 @@
           <t>X &lt; -0.02212</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>53~53</t>
-        </is>
+      <c r="B7" t="n">
+        <v>53</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>2.223542811865492</v>
@@ -4075,10 +4011,8 @@
           <t>X &lt; -0.02046</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>63~63</t>
-        </is>
+      <c r="B8" t="n">
+        <v>63</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>1.474815648043993</v>
@@ -4129,10 +4063,8 @@
           <t>X &lt; -0.01879</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>77~77</t>
-        </is>
+      <c r="B9" t="n">
+        <v>77</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-0.5453863721580348</v>
@@ -4183,10 +4115,8 @@
           <t>X &lt; -0.01713</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>98~98</t>
-        </is>
+      <c r="B10" t="n">
+        <v>98</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-0.4526219936793581</v>
@@ -4237,10 +4167,8 @@
           <t>X &lt; -0.01546</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>122~122</t>
-        </is>
+      <c r="B11" t="n">
+        <v>122</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-1.673766189062434</v>
@@ -4291,10 +4219,8 @@
           <t>X &lt; -0.01379</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>150~150</t>
-        </is>
+      <c r="B12" t="n">
+        <v>150</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-2.493438320209975</v>
@@ -4345,10 +4271,8 @@
           <t>X &lt; -0.01213</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>193~193</t>
-        </is>
+      <c r="B13" t="n">
+        <v>193</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-0.1618321025934009</v>
@@ -4399,10 +4323,8 @@
           <t>X &lt; -0.01046</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>247~247</t>
-        </is>
+      <c r="B14" t="n">
+        <v>247</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>0.9478572263487308</v>
@@ -4453,10 +4375,8 @@
           <t>X &lt; -0.008795</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>312~312</t>
-        </is>
+      <c r="B15" t="n">
+        <v>312</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>2.314253987482338</v>
@@ -4507,10 +4427,8 @@
           <t>X &lt; -0.007129</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>400~400</t>
-        </is>
+      <c r="B16" t="n">
+        <v>400</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>2.506561679790032</v>
@@ -4561,10 +4479,8 @@
           <t>X &lt; -0.005462</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>480~480</t>
-        </is>
+      <c r="B17" t="n">
+        <v>480</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>1.673228346456689</v>
@@ -4615,10 +4531,8 @@
           <t>X &lt; -0.003796</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>571~572</t>
-        </is>
+      <c r="B18" t="n">
+        <v>571</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>2.052016225244564</v>
@@ -4669,10 +4583,8 @@
           <t>X &lt; -0.00213</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>655~656</t>
-        </is>
+      <c r="B19" t="n">
+        <v>655</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>2.689488509058322</v>
@@ -4723,10 +4635,8 @@
           <t>X &lt; -0.0004641</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>754~755</t>
-        </is>
+      <c r="B20" t="n">
+        <v>754</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>2.738349759260224</v>
@@ -4777,10 +4687,8 @@
           <t>X &lt; 0.001202</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>838~839</t>
-        </is>
+      <c r="B21" t="n">
+        <v>838</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>2.572115911017676</v>
@@ -4831,10 +4739,8 @@
           <t>X &lt; 0.002868</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>941~942</t>
-        </is>
+      <c r="B22" t="n">
+        <v>941</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>1.965160405904676</v>
@@ -4885,10 +4791,8 @@
           <t>X &lt; 0.004534</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1039~1040</t>
-        </is>
+      <c r="B23" t="n">
+        <v>1039</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>1.737330910559251</v>
@@ -4939,10 +4843,8 @@
           <t>X &lt; 0.0062</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1136~1138</t>
-        </is>
+      <c r="B24" t="n">
+        <v>1136</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>1.372994017224123</v>
@@ -4993,10 +4895,8 @@
           <t>X &lt; 0.007867</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1225~1228</t>
-        </is>
+      <c r="B25" t="n">
+        <v>1225</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>1.57822291757504</v>
@@ -5047,10 +4947,8 @@
           <t>X &lt; 0.009533</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>1304~1308</t>
-        </is>
+      <c r="B26" t="n">
+        <v>1304</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>1.099833851043847</v>
@@ -5101,10 +4999,8 @@
           <t>X &lt; 0.0112</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>1369~1373</t>
-        </is>
+      <c r="B27" t="n">
+        <v>1369</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>1.257472094939338</v>
@@ -5155,10 +5051,8 @@
           <t>X &lt; 0.01286</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>1420~1425</t>
-        </is>
+      <c r="B28" t="n">
+        <v>1420</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>0.7697195745268672</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 0.01453</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>1470~1475</t>
-        </is>
+      <c r="B29" t="n">
+        <v>1470</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>1.133680323857817</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 0.0162</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>1501~1506</t>
-        </is>
+      <c r="B30" t="n">
+        <v>1501</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>1.158620112724947</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 0.01786</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>1520~1525</t>
-        </is>
+      <c r="B31" t="n">
+        <v>1520</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>1.080332171593298</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 0.01953</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>1538~1543</t>
-        </is>
+      <c r="B32" t="n">
+        <v>1538</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>1.168259670716793</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 0.0212</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>1551~1556</t>
-        </is>
+      <c r="B33" t="n">
+        <v>1551</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>0.9769986977848788</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 0.02286</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>1562~1567</t>
-        </is>
+      <c r="B34" t="n">
+        <v>1562</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>1.048361296892772</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 0.02453</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>1573~1578</t>
-        </is>
+      <c r="B35" t="n">
+        <v>1573</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>0.9286149117291842</v>

--- a/workspaces/btc_daily_14days/dxy/dxy_ret_10.xlsx
+++ b/workspaces/btc_daily_14days/dxy/dxy_ret_10.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that DXY Ret-10 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that DXY Ret-10 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -568,1509 +568,1509 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.02295</t>
+          <t>X ≈ -0.02269</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-2.482862869248386</v>
+        <v>9.028688666340557</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-4.092875363367554</v>
+        <v>-7.914750916950013</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-4.487581162988704</v>
+        <v>7.032509323390798</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.6295009405076328</v>
+        <v>11.00119653469334</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.09417495800476416</v>
+        <v>14.30438552520305</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.3894176827469948</v>
+        <v>6.927427154560746</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.304683965474716</v>
+        <v>6.844589100417913</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>19.7990624917125</v>
+        <v>21.74171020834776</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>4.769044987806268</v>
+        <v>6.320392606616871</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>8.915265436422871</v>
+        <v>9.315195687033992</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>8.710838759377864</v>
+        <v>9.112905382983584</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>8.750007834304398</v>
+        <v>9.149544203020035</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>3.335726250299111</v>
+        <v>4.886538564182459</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>8.585447582575398</v>
+        <v>12.80578717764997</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.02129</t>
+          <t>X ≈ -0.02105</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-2.48265791864867</v>
+        <v>3.064637373141565</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-14.06678351004353</v>
+        <v>1.45936146645024</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-34.40977315761836</v>
+        <v>-6.321613498925302</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-34.28001822340291</v>
+        <v>-6.192967846874126</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-34.81528418200497</v>
+        <v>-14.12258761095242</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-34.54266463677752</v>
+        <v>-17.52564442293777</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-4.685613101784632</v>
+        <v>-6.522663990338671</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-5.15317063133552</v>
+        <v>0.4055259390551882</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>4.768900692167655</v>
+        <v>4.043912226707533</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-16.05258735823993</v>
+        <v>-4.20427299222559</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-6.269952676439331</v>
+        <v>-4.409883002122598</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-6.240393196009641</v>
+        <v>-0.674700503279702</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-16.66427374970203</v>
+        <v>-4.797684532565427</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-6.414552417424602</v>
+        <v>-8.276833904974609</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.01963</t>
+          <t>X ≈ -0.01939</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-9.602064595173701</v>
+        <v>3.604712686579205</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-4.092277650840494</v>
+        <v>-5.295460767147354</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>9.761798742203268</v>
+        <v>4.038553485629166</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-4.356893224829584</v>
+        <v>-0.6960913304638225</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>2.232109764763379</v>
+        <v>-3.666861791125754</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-4.600347005218552</v>
+        <v>-3.370955106808594</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-11.81433053901026</v>
+        <v>-1.021730968590326</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-19.41076375430876</v>
+        <v>-8.794742914692762</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-5.218154704636724</v>
+        <v>-1.549886262354384</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-13.19884672643217</v>
+        <v>-7.272490932993087</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-20.53687256669502</v>
+        <v>-7.47888481963782</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-20.51671353603188</v>
+        <v>-9.884171071535654</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-6.664273749700079</v>
+        <v>-0.5530191019764175</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-6.414552417425412</v>
+        <v>-2.766445467756895</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.01796</t>
+          <t>X ≈ -0.01774</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.1089364773417643</v>
+        <v>2.228392565997858</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>12.53059208011995</v>
+        <v>10.02867245569173</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-6.861332577217823</v>
+        <v>7.755467566640803</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-1.981944884647135</v>
+        <v>2.241731823674996</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-7.266566964641861</v>
+        <v>-0.1771658422255982</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-2.223884210544533</v>
+        <v>3.885522981272729</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>7.196023446765444</v>
+        <v>0.03488282694308253</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-7.528770003483046</v>
+        <v>-2.315578267573002</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-7.59582905735261</v>
+        <v>3.276059643476145</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-13.19843740286463</v>
+        <v>-1.341849687326594</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-3.891649471423925</v>
+        <v>0.338577088861058</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-13.37828791142913</v>
+        <v>-1.512788259713538</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-9.045226130653276</v>
+        <v>-1.933245081451545</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-8.795504798376989</v>
+        <v>-3.594793373878325</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.0163</t>
+          <t>X ≈ -0.01609</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-6.634461622324849</v>
+        <v>-4.466307618938174</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-4.092211113921408</v>
+        <v>-3.414832536082386</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-8.641656824557103</v>
+        <v>-2.480252187181087</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-4.356293320442617</v>
+        <v>1.639339277276797</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.7358705917236321</v>
+        <v>3.763362903671208</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.4415979572268895</v>
+        <v>4.061012204889622</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.5268657538801875</v>
+        <v>6.639270193673077</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>7.322605326609157</v>
+        <v>3.511964573252413</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>7.265356981207049</v>
+        <v>7.446622202718054</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>2.257470913889549</v>
+        <v>6.599657400555493</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>6.213954624562454</v>
+        <v>6.396755844508391</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>2.087741141313991</v>
+        <v>6.432808947649271</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>1.66905958363197</v>
+        <v>4.681410655529447</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>1.918780915909203</v>
+        <v>3.575017946877246</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.01462</t>
+          <t>X ≈ -0.01443</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>93</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-6.040347918270996</v>
+        <v>-3.008319748200712</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-4.09175519433186</v>
+        <v>-4.614840328196841</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-4.485519172691994</v>
+        <v>-3.938067936392919</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-7.917462239818697</v>
+        <v>-1.663903285841926</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-4.890925434564096</v>
+        <v>-1.128554387620063</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-1.035528645583881</v>
+        <v>-1.905179336787967</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>6.007354502155373</v>
+        <v>-0.9171136159316546</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.588137154669731</v>
+        <v>-0.3101467481870017</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.651363320622799</v>
+        <v>3.923980425766601</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-2.497980685981659</v>
+        <v>5.224471222155444</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-13.40223017662151</v>
+        <v>-0.3507828559560906</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-6.239928818948428</v>
+        <v>6.131746748189684</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-10.23570232112905</v>
+        <v>5.713341215065704</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-2.843123845996033</v>
+        <v>8.091146979135793</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.01296</t>
+          <t>X ≈ -0.01279</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>7.947930446230586</v>
+        <v>1.881454052213968</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1.706450527282421</v>
+        <v>4.147336250425454</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1.312741902277949</v>
+        <v>3.754240974222988</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.44260834102159</v>
+        <v>-0.955704385200427</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>7.864523801411579</v>
+        <v>5.286587715773109</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>10.48504541758405</v>
+        <v>7.522223549469786</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>8.07878611178409</v>
+        <v>5.501456365509142</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>9.932402241191546</v>
+        <v>5.036593537773662</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>9.87720609187091</v>
+        <v>7.885295863947405</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>9.030764737250948</v>
+        <v>6.068849862120743</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>4.181810475539777</v>
+        <v>6.836163286745418</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>6.541928484205805</v>
+        <v>6.872372170726138</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>1.475261134020045</v>
+        <v>5.483652868092548</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>6.37614525699427</v>
+        <v>8.623561636197188</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.01129</t>
+          <t>X ≈ -0.01113</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>54</v>
+        <v>142</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>4.899741395413976</v>
+        <v>0.3346732716899439</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-7.783452446847406</v>
+        <v>4.34404044542724</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.7914096451593196</v>
+        <v>1.845015021630026</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-6.200822376853118</v>
+        <v>1.2739138514589</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1.197092446443072</v>
+        <v>4.951544152760327</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.943911745060511</v>
+        <v>6.654754385715066</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>6.401718907351984</v>
+        <v>9.383351623761698</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.3912168595250023</v>
+        <v>3.295514629859611</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.3294239262902394</v>
+        <v>6.047935369130848</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>5.030636746210469</v>
+        <v>6.607897263228523</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>6.675637075974223</v>
+        <v>5.701768436191372</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>6.713728316661737</v>
+        <v>8.553086423343096</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>8.15054106511392</v>
+        <v>7.431576937530963</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.9928549899825967</v>
+        <v>6.251074284905577</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.009628</t>
+          <t>X ≈ -0.009476</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>65</v>
+        <v>148</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>7.481051418118035</v>
+        <v>8.29780624057792</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>4.346616645168808</v>
+        <v>-0.03828359785476465</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>7.019641160537283</v>
+        <v>2.261858014514594</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>7.150120387356374</v>
+        <v>3.066953960093819</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>8.147906725378604</v>
+        <v>2.530188087927755</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>5.377980908529757</v>
+        <v>1.479181033366771</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>6.826791613949894</v>
+        <v>1.394867560945478</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>7.895020723819506</v>
+        <v>4.301978889506479</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>9.375032313759469</v>
+        <v>2.217632251497243</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>11.60105044550696</v>
+        <v>6.093932128726244</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>8.324689322052663</v>
+        <v>5.216415633943377</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>5.289847630404843</v>
+        <v>3.226532730823294</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>1.797264711837578</v>
+        <v>3.483184531599555</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>8.200832197960011</v>
+        <v>7.764207136066126</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.007962</t>
+          <t>X ≈ -0.007826</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>88</v>
+        <v>193</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>3.177475577685847</v>
+        <v>0.3656949720400178</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.6903816691952613</v>
+        <v>0.3104673921849681</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.179963748926234</v>
+        <v>-0.599858446680372</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.4430786268763</v>
+        <v>1.596743711753859</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.907204241637508</v>
+        <v>2.609701448212846</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>4.469701570790221</v>
+        <v>0.8396572686443236</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>4.383245994905629</v>
+        <v>2.306178971280126</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>3.916445231371512</v>
+        <v>3.392584646143547</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>9.529983043875596</v>
+        <v>2.297548222989406</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>9.818555820807291</v>
+        <v>4.037126075030159</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>13.01814345946751</v>
+        <v>7.457837399068168</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>15.33338429034599</v>
+        <v>6.976899188936123</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>11.51754443211728</v>
+        <v>3.451554194126558</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>12.90362940075723</v>
+        <v>2.642375459830738</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.006295</t>
+          <t>X ≈ -0.006174</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>80</v>
+        <v>237</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-2.480843779012787</v>
+        <v>-1.421762858573125</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-4.086581449739768</v>
+        <v>-1.764779406272893</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-6.973185693526261</v>
+        <v>-0.477739322041387</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-6.842932560918761</v>
+        <v>0.9140208092780284</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-6.13285308119103</v>
+        <v>-2.567972589613397</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-8.338663849886501</v>
+        <v>-3.534492813981132</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-7.178697169125506</v>
+        <v>-2.778752285703263</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-5.152084041852454</v>
+        <v>-1.561116078755553</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-10.21054882080789</v>
+        <v>-1.62299473827732</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-6.064842433810171</v>
+        <v>0.05613459657750752</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-7.516792343539279</v>
+        <v>-1.412515603166369</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-6.240380206146881</v>
+        <v>-2.221577809333994</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-4.164273749701032</v>
+        <v>-0.1109768666387794</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-5.164552417424609</v>
+        <v>0.1151023350629004</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.004629</t>
+          <t>X ≈ -0.004521</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>91</v>
+        <v>228</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>4.052936395798454</v>
+        <v>1.003773236471147</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-6.341437842934006</v>
+        <v>-1.490925789718261</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-6.736306549530596</v>
+        <v>-2.324044068404518</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-5.510328332758547</v>
+        <v>-1.756777469953676</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-2.767999401256041</v>
+        <v>-1.860780783768945</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-2.463079908245334</v>
+        <v>-1.562532655007175</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.847319587072114</v>
+        <v>0.9807743759412517</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.2833544743439163</v>
+        <v>3.576854112464204</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.379316467918436</v>
+        <v>0.2520933387809663</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>3.259254321808157</v>
+        <v>0.5159598314735092</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.2349892505956035</v>
+        <v>0.312226002547753</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.8961829215881565</v>
+        <v>0.7854087182247156</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.818119903546922</v>
+        <v>-0.5106221164785225</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.568398571270755</v>
+        <v>-2.039017140842148</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.002963</t>
+          <t>X ≈ -0.002868</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>84</v>
+        <v>252</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>7.001969999883826</v>
+        <v>0.2933947299647457</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1.848342797310174</v>
+        <v>-3.2846310887182</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.2667415360564718</v>
+        <v>-1.703261813850268</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.3966917154761589</v>
+        <v>-2.365177186087344</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.326644335127149</v>
+        <v>-2.111778882851155</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.035441490562548</v>
+        <v>-1.419884514863746</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.123008467469745</v>
+        <v>0.07798330047592827</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.777967304983683</v>
+        <v>1.196304191442891</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-6.405733894062756</v>
+        <v>0.7389012933583032</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>2.252618077102966</v>
+        <v>1.474605969036055</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>2.049483758291146</v>
+        <v>-0.3139244374792796</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-2.671982215878813</v>
+        <v>-0.6756998465083157</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-3.09284517827232</v>
+        <v>1.681421741441298</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-2.843123845995898</v>
+        <v>-0.07577570391631383</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.001297</t>
+          <t>X ≈ -0.001216</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>99</v>
+        <v>275</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>3.046187521808484</v>
+        <v>-4.099525777069864</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>2.459674989010082</v>
+        <v>-4.976327501066876</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2.065174078213346</v>
+        <v>-5.3736503678575</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.8246109730703708</v>
+        <v>-5.246109434159884</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>3.672326362608345</v>
+        <v>-2.52331114664689</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.952574986375254</v>
+        <v>-3.678471777946001</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.864400882403451</v>
+        <v>-3.040836684863265</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-2.633232768423532</v>
+        <v>-4.96069954804922</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-5.720142117478801</v>
+        <v>-7.199745242760315</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.535639438040391</v>
+        <v>-5.145062873561045</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.722955959171216</v>
+        <v>-5.713784365360709</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>3.345616566320025</v>
+        <v>-4.954787687181252</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>5.961988876561797</v>
+        <v>-6.103191216362127</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.869097871970119</v>
+        <v>-6.243163871304574</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.0003689</t>
+          <t>X ≈ 0.000436</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>84</v>
+        <v>243</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.068564903431998</v>
+        <v>1.615685099293827</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.70897644887318</v>
+        <v>-1.222054158357388</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-9.218453986236817</v>
+        <v>-3.667238469790718</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2.771149207645742</v>
+        <v>1.791405322744936</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.323893782356613</v>
+        <v>1.253594792768034</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.340304131262329</v>
+        <v>1.1412347387881</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-7.06037593474322</v>
+        <v>1.058710108651667</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-6.338350415978468</v>
+        <v>-1.238880144611066</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-7.589167510713409</v>
+        <v>-1.299582230929481</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-6.06117900615218</v>
+        <v>-4.20261770535182</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-12.20102768008529</v>
+        <v>-5.229660568728917</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-13.37293808575143</v>
+        <v>-3.142144697014224</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-13.8071308925581</v>
+        <v>-3.56297906131806</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-7.605028607900863</v>
+        <v>-1.692471765056816</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.002035</t>
+          <t>X ≈ 0.002089</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>103</v>
+        <v>272</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-2.96667885444058</v>
+        <v>-4.854244762675144</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.2742975224111461</v>
+        <v>-2.805398328028105</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.816533413615389</v>
+        <v>-3.934819276776729</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.9574141189723875</v>
+        <v>-3.441293937217814</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.4401042785514022</v>
+        <v>-3.982055668896031</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.206771569357365</v>
+        <v>-4.420536087858018</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-4.198119058296186</v>
+        <v>-5.240187785909086</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-3.695392758037528</v>
+        <v>-5.708221144710272</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-4.727081174623585</v>
+        <v>-4.668522250124091</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-5.573701618515678</v>
+        <v>-4.051252197647628</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-7.710096611596505</v>
+        <v>-6.095642045954399</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-9.629848438961574</v>
+        <v>-7.325897785197093</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-8.120584429312537</v>
+        <v>-7.749436837186231</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-8.841736883444021</v>
+        <v>-8.998511464887542</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.003701</t>
+          <t>X ≈ 0.003741</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>98</v>
+        <v>232</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.4538293907923858</v>
+        <v>0.7375515865778652</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.007207237506933</v>
+        <v>2.131080247034994</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>3.661390802307402</v>
+        <v>3.453243899904344</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.772666851487806</v>
+        <v>1.00786899718716</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.221571736096024</v>
+        <v>0.03944790152847588</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2.526905303021664</v>
+        <v>2.056886801327529</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-2.644043780080104</v>
+        <v>1.114984856145895</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-6.159583743737599</v>
+        <v>-0.6451385903139411</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.156459528275086</v>
+        <v>1.01563248443145</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-4.018663409079323</v>
+        <v>1.025894352046862</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.166101554681944</v>
+        <v>-0.2295768635831621</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-3.177610174459637</v>
+        <v>0.2347450343015112</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.562232933374368</v>
+        <v>1.107465061895404</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.748712888697845</v>
+        <v>2.626742084808285</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.005367</t>
+          <t>X ≈ 0.005393</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>97</v>
+        <v>254</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-2.500612518015835</v>
+        <v>-0.7141621031353722</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>2.009925944457123</v>
+        <v>0.02787517609840506</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>7.772299023085331</v>
+        <v>2.767806765254882</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>2.773985062615125</v>
+        <v>-0.6323269265745353</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.204773960016148</v>
+        <v>-2.743319985628702</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-6.711847506952068</v>
+        <v>-4.413575242719517</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-2.683059951276178</v>
+        <v>-6.46634860067757</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.10280918321984</v>
+        <v>-3.789237119828421</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-2.178199683184587</v>
+        <v>-5.02947405080193</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-4.071412311645538</v>
+        <v>-3.912969675248512</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-7.37673113661144</v>
+        <v>-2.155527152191667</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-4.687080267804014</v>
+        <v>-4.086502299077999</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-5.117881997123575</v>
+        <v>-3.497858158835186</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-6.930016334950373</v>
+        <v>-6.031281265721226</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.007033</t>
+          <t>X ≈ 0.007046</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>89</v>
+        <v>234</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>4.199710556210057</v>
+        <v>3.683085612549597</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>4.794713972935938</v>
+        <v>3.353985188083435</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.045161391614947</v>
+        <v>0.8321939498355917</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>3.414903188062056</v>
+        <v>3.517587598822928</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>2.867383730919734</v>
+        <v>0.4212836895481828</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>3.177031279365231</v>
+        <v>2.424711752425566</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.975858715746469</v>
+        <v>3.19877091315054</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>4.867534068366446</v>
+        <v>5.294010751067681</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.913568873709359</v>
+        <v>3.096635274272558</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.5427441314965833</v>
+        <v>0.1110407906296587</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>4.83946788209942</v>
+        <v>1.182291034265475</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>2.660057771475621</v>
+        <v>2.499438101631533</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>4.009883553669901</v>
+        <v>1.221715861779437</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>7.630391402800115</v>
+        <v>2.976727348586749</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.0087</t>
+          <t>X ≈ 0.008699</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>79</v>
+        <v>211</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-6.289319610424485</v>
+        <v>-2.976161598263928</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>10.99207866262403</v>
+        <v>5.759049065564831</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>6.803055273808582</v>
+        <v>3.949452510561777</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>5.670799293817481</v>
+        <v>1.722205496633066</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3.849986932877535</v>
+        <v>3.806543248471364</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>7.414709671176368</v>
+        <v>2.95392749232294</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>1.000862029853458</v>
+        <v>-1.601705527112486</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1.799501415882091</v>
+        <v>-0.1730395737428267</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>4.270147099320035</v>
+        <v>1.187779217601701</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>7.217490268722493</v>
+        <v>1.759661369139131</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>7.012736944404871</v>
+        <v>0.1331592630116489</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>4.515474532130092</v>
+        <v>-0.3063962339221362</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>2.829397136375057</v>
+        <v>-0.252613437946394</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>5.610764038271597</v>
+        <v>1.394923160147329</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.01037</t>
+          <t>X ≈ 0.01035</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>4.41095024405049</v>
+        <v>1.559066512351173</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>5.894988066825789</v>
+        <v>2.434016571889131</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.6537267936169755</v>
+        <v>0.7887632208692992</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>5.630372492836678</v>
+        <v>3.768351635235099</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>6.630412816226006</v>
+        <v>7.605062082139412</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>6.927854753941709</v>
+        <v>8.527436111774534</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>5.30465949820789</v>
+        <v>4.692725752508331</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>7.914399176349463</v>
+        <v>3.600657108721627</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>4.776476213244088</v>
+        <v>5.414674952198844</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>3.92635102821616</v>
+        <v>5.189756155868999</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>6.798520780821654</v>
+        <v>8.735054997608799</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>5.294442399705552</v>
+        <v>9.394433149964094</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>4.874187788760651</v>
+        <v>8.349282296650713</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>6.662370659498428</v>
+        <v>4.200017946877239</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.01203</t>
+          <t>X ≈ 0.01201</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>51</v>
+        <v>128</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-12.32207565749785</v>
+        <v>-6.004639881735407</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-9.006972717488011</v>
+        <v>2.50719395148711</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-5.480272796633599</v>
+        <v>-2.14312350835322</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.532333277150407</v>
+        <v>2.674601635235184</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.006087937921705588</v>
+        <v>-0.2074379178605312</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-1.669430313931571</v>
+        <v>2.433686111774534</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>8.049757537423609</v>
+        <v>5.473975752508387</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>3.661005511191121</v>
+        <v>1.100657108721627</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1.639221311283301</v>
+        <v>0.2584249521988298</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.171688187470146</v>
+        <v>-2.935243844131008</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.5843428019377939</v>
+        <v>-1.577445002391201</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.342058354442258</v>
+        <v>-3.105566850035835</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.76231296538716</v>
+        <v>-0.4007177033492866</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>4.369761308065648</v>
+        <v>4.512517946877225</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.01369</t>
+          <t>X ≈ 0.01366</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>11.50656167979002</v>
+        <v>4.312432776788256</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>3.894988066825796</v>
+        <v>-2.09210212359816</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>5.500119360229178</v>
+        <v>1.513126491646752</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-6.369627507163322</v>
+        <v>-3.95664836476486</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>1.09195127776448</v>
+        <v>-0.4949379178605255</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-2.610606784519831</v>
+        <v>-3.397563888225463</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.6953405017921597</v>
+        <v>-3.48227424749161</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.8374760994263255</v>
+        <v>-5.549342891278371</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-1.223523786755941</v>
+        <v>-8.810325047801122</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>3.926351028216189</v>
+        <v>-4.060243844131008</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>1.72159770389861</v>
+        <v>-7.464945002391204</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>1.755980861244041</v>
+        <v>-4.230566850035878</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-2.664273749700889</v>
+        <v>-3.850717703349261</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>3.585447582575398</v>
+        <v>-2.024982053122727</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.01537</t>
+          <t>X ≈ 0.0153</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>31</v>
+        <v>83</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2.345271357209377</v>
+        <v>4.134098984480659</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>7.185310647470928</v>
+        <v>7.353681008931936</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>13.2420548441002</v>
+        <v>11.77818673261064</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>10.14650152509474</v>
+        <v>8.293954044873701</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>9.608080310022615</v>
+        <v>6.550845214669529</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>6.679715796125265</v>
+        <v>9.257857798521513</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>3.369175627240217</v>
+        <v>6.763508885038483</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>2.901992228458717</v>
+        <v>7.50125951836015</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>6.066798793889298</v>
+        <v>9.8499159160543</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>8.442480060474196</v>
+        <v>7.795177842615999</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>14.68933963938241</v>
+        <v>12.40975379278956</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>11.49791634511493</v>
+        <v>10.03449339092794</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>4.626048830944271</v>
+        <v>8.409523260506106</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>4.875770163220558</v>
+        <v>6.225620356515805</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.01703</t>
+          <t>X ≈ 0.01696</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-5.1250172675784</v>
+        <v>-6.307331124873961</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-11.9997487752795</v>
+        <v>-6.922290802843435</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>3.394856202334473</v>
+        <v>2.116900076552497</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-12.26436434926859</v>
+        <v>-5.300044591179926</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-7.539627669603917</v>
+        <v>-5.838334144275592</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-12.50534362662502</v>
+        <v>-3.654167661810391</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-17.85323523863422</v>
+        <v>-7.512462926736916</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-23.58357653215259</v>
+        <v>-9.866324023353762</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-13.11826062886121</v>
+        <v>-6.153721274216295</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-13.96838581388903</v>
+        <v>-10.7772249762065</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-19.43629703294349</v>
+        <v>-7.208341228806347</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-14.13875598086128</v>
+        <v>-3.400378170790539</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-9.295852697069272</v>
+        <v>-0.04694411844359081</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-9.046131364793027</v>
+        <v>-7.368378279537822</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 0.01869</t>
+          <t>X ≈ 0.01861</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>8.617672790901153</v>
+        <v>3.07463952502124</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>23.67276584460355</v>
+        <v>1.463453431957333</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>17.72234158245136</v>
+        <v>3.846459824980116</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>23.40815027061441</v>
+        <v>12.31001830190177</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>22.86972905554224</v>
+        <v>14.54950652658389</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>12.0560598821468</v>
+        <v>9.291325000663463</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.8602150537634472</v>
+        <v>3.651059085841702</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>5.948587210537539</v>
+        <v>8.739545997610477</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.3320317687996805</v>
+        <v>3.123008285532187</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.5180934162282824</v>
+        <v>-3.28246606635323</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>4.832708815009653</v>
+        <v>-0.7093894468356439</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-6.244019138755945</v>
+        <v>-6.230566850035878</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-6.664273749700925</v>
+        <v>-3.872939925571551</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>15.80766980479761</v>
+        <v>1.908351280210582</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 0.02037</t>
+          <t>X ≈ 0.02026</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-21.72420755097923</v>
+        <v>-10.54543215956666</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-23.33578116394346</v>
+        <v>-8.930811801017583</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-31.42295756284775</v>
+        <v>-15.77719608899838</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-8.215781353317091</v>
+        <v>-9.195358042184218</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>6.630412816226105</v>
+        <v>-3.282034692054104</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.7644529383659844</v>
+        <v>-2.984660662418996</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.8491866556382917</v>
+        <v>0.1564354299277184</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>6.375937637887901</v>
+        <v>6.140979689366745</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>6.314937751705628</v>
+        <v>2.854191081231072</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>5.464812566677672</v>
+        <v>2.004272284901255</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>5.260059242360121</v>
+        <v>1.799571126641062</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>5.294442399705552</v>
+        <v>1.833949278996343</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>4.874187788760672</v>
+        <v>1.413798425682977</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-2.568398571270755</v>
+        <v>1.639534075909509</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.02203</t>
+          <t>X ≈ 0.02192</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>11.14292531615366</v>
+        <v>8.388649186856959</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.4404426122803073</v>
+        <v>2.429637006836664</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.04557390568371744</v>
+        <v>2.034865622081561</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.1758270382912173</v>
+        <v>2.165090765669923</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.3625941767809522</v>
+        <v>10.32245338648728</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-9.156061329974378</v>
+        <v>1.924175242209287</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.1498859563375703</v>
+        <v>6.187290969899678</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.6170693551190993</v>
+        <v>14.41587450002604</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>8.412839849607721</v>
+        <v>18.70271843045978</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>7.562714664579765</v>
+        <v>13.50497354717334</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>7.357961340262214</v>
+        <v>13.30027238891314</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-1.698564593301448</v>
+        <v>13.33465054126854</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>6.972089886662715</v>
+        <v>17.26232577491157</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-1.869097871970062</v>
+        <v>13.14023533818153</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.0237</t>
+          <t>X ≈ 0.02357</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-16.12980195657361</v>
+        <v>-16.11727966689799</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.4404426122803073</v>
+        <v>-17.72846575996181</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>9.136482996592846</v>
+        <v>-4.48687350835322</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-8.915082052617905</v>
+        <v>-17.99301200112849</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-18.5444123585991</v>
+        <v>-23.07675609967874</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-9.156061329974342</v>
+        <v>-27.32483661549822</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.1498859563375703</v>
+        <v>-18.31863788385527</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-9.707978446028122</v>
+        <v>-23.33116107309656</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-9.768978332210459</v>
+        <v>-14.30123413871024</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-1.5281944263293</v>
+        <v>-10.60569838958556</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-1.732947750646879</v>
+        <v>-10.81039954784575</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-19.88038277511962</v>
+        <v>-19.86693048639955</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-20.30063738606452</v>
+        <v>-15.74162679425837</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-20.05091605378821</v>
+        <v>-20.06134568948639</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that DXY Ret-10 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that DXY Ret-10 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2210,1561 +2210,1561 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.02379</t>
+          <t>X &gt; -0.02352</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1573</v>
+        <v>4084</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.8018721994351452</v>
+        <v>0.02091457722742973</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.619147863908843</v>
+        <v>0.03387443890181885</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.2876906982126854</v>
+        <v>-0.005799027278740709</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.2911207490192993</v>
+        <v>0.1377336577070523</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.9575188110555715</v>
+        <v>0.1258292455892374</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.4020835708101202</v>
+        <v>0.09451822321148029</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.3173498535378414</v>
+        <v>0.1209523474729295</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.08638176859390967</v>
+        <v>0.08293094735243756</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-1.001301564533684</v>
+        <v>0.03545631683567763</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.30730340916854</v>
+        <v>0.006292359391501634</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.356518338819221</v>
+        <v>-0.03788358815092607</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.5261030015260033</v>
+        <v>0.01025547008160288</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.9109361781815011</v>
+        <v>-0.004450873483918372</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.3559498076230767</v>
+        <v>0.03926868145119755</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.02212</t>
+          <t>X &gt; -0.02187</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1553</v>
+        <v>4058</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.8441740032816796</v>
+        <v>-0.03679910594579638</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.6798307129400882</v>
+        <v>0.08480205330599233</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.3491880821302757</v>
+        <v>-0.05089415224606597</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.2867629873774646</v>
+        <v>0.06813039629708584</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.9686372122539098</v>
+        <v>0.03498585887905392</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.4022466859171843</v>
+        <v>0.05073911226641314</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.3175129686449054</v>
+        <v>0.07787335398437989</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.342472486691868</v>
+        <v>-0.05583895427050578</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-1.075613818910249</v>
+        <v>-0.004811880191006424</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.196447491238672</v>
+        <v>-0.05335068805025855</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.2489288936091896</v>
+        <v>-0.09651358155888801</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.6455635403003868</v>
+        <v>-0.0483008401836571</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.9656259712076505</v>
+        <v>-0.03578791768779155</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.2499678658980002</v>
+        <v>-0.04252764208283821</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.02046</t>
+          <t>X &gt; -0.02022</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1543</v>
+        <v>4031</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.8657348064050154</v>
+        <v>-0.05757280600418113</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.7754017707688874</v>
+        <v>0.07559513091580072</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.5744567875077848</v>
+        <v>-0.008892310926206903</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.5107861967797973</v>
+        <v>0.1100677946016333</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1.200548562832381</v>
+        <v>0.1298145573869789</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.6287205117285524</v>
+        <v>0.1684673076150958</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.3499376353359622</v>
+        <v>0.1220843458714214</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.3112949225658497</v>
+        <v>-0.05892921775842552</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-1.113491424296363</v>
+        <v>-0.03193059785071029</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.3017555589604939</v>
+        <v>-0.02554743768739343</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.2911769919244733</v>
+        <v>-0.06762224582204368</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.6093041128492516</v>
+        <v>-0.04410515898702982</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.8638848968168915</v>
+        <v>-0.003892306523894717</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.293159831441244</v>
+        <v>0.01262648073980444</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.01879</t>
+          <t>X &gt; -0.01857</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1529</v>
+        <v>3990</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.9615812365044931</v>
+        <v>-0.09520531357208029</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.8199717589327449</v>
+        <v>0.1307864321239549</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.490334624417045</v>
+        <v>-0.05048260607878774</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.5553561849436548</v>
+        <v>0.1183516352351361</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>1.191103267327456</v>
+        <v>0.1688280236248261</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.6765994817987036</v>
+        <v>0.2048373123748348</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.4613174616543674</v>
+        <v>0.1338378365714163</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.1364142399992048</v>
+        <v>0.03083728890180737</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-1.075907849460023</v>
+        <v>-0.01633255718788718</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.425371276419952</v>
+        <v>0.04891990148742309</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.4818850977587985</v>
+        <v>0.008533585136966337</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.4270256747036996</v>
+        <v>0.05700830026472659</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.810774730734245</v>
+        <v>0.001750349770233584</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.354577733000518</v>
+        <v>0.0411833604110754</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.01713</t>
+          <t>X &gt; -0.01691</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1508</v>
+        <v>3937</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.9764889765514226</v>
+        <v>-0.1264856507875223</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.656892828730534</v>
+        <v>-0.002459176016522235</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.592711952821773</v>
+        <v>-0.1555665174717618</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.5906899531541399</v>
+        <v>0.0897666339683596</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1.30888249469573</v>
+        <v>0.1734858023624639</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.7169908329520354</v>
+        <v>0.1552878228011494</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.3675317682277495</v>
+        <v>0.1351699715753014</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.03347029369074761</v>
+        <v>0.062424798298089</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.9851131907294217</v>
+        <v>-0.06065482963777669</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.6150927500704668</v>
+        <v>0.06764247913719856</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.5427897568787117</v>
+        <v>0.004090530603725995</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.2466699008500868</v>
+        <v>0.07814094382042924</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.6961039884276801</v>
+        <v>0.02779931036326388</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.4819993067133339</v>
+        <v>0.09013097710330698</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.01546</t>
+          <t>X &gt; -0.01526</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1484</v>
+        <v>3862</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1.099577126398486</v>
+        <v>-0.04220635311499166</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.73369774424512</v>
+        <v>0.06380907929288782</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.7420548441001387</v>
+        <v>-0.1104211458435316</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.6706950734818378</v>
+        <v>0.05967394928473624</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1.341951277764508</v>
+        <v>0.1037704262365864</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.7357281179684065</v>
+        <v>0.07943869575386486</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.3819964181809894</v>
+        <v>0.008860412627257119</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.1524364762292905</v>
+        <v>-0.004565228403507149</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.118543975181218</v>
+        <v>-0.2064460718507988</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.5885313781488577</v>
+        <v>-0.05920918298253497</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.451072804840706</v>
+        <v>-0.1200549635813672</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.2844231791600222</v>
+        <v>-0.0452666429965447</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.7343546122345757</v>
+        <v>-0.06257377376088158</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.458762946456801</v>
+        <v>0.02245450824441519</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.01379</t>
+          <t>X &gt; -0.01361</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1456</v>
+        <v>3769</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.236883377257513</v>
+        <v>0.03098243588552663</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.8264949161408381</v>
+        <v>0.1792546603214191</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.8425851136538327</v>
+        <v>-0.01597403745375203</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.8358519448914734</v>
+        <v>0.1022031832637182</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.461814291463135</v>
+        <v>0.1341780164962429</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.7697907480367121</v>
+        <v>0.128409106214562</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.2738164550276352</v>
+        <v>0.03170880335582638</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.1248268477977419</v>
+        <v>0.002974989516324911</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.108297449307351</v>
+        <v>-0.3083642634874195</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.6478873793821407</v>
+        <v>-0.1895838918384101</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.7174824775611341</v>
+        <v>-0.1143617574283198</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.1698942245487061</v>
+        <v>-0.1976843255065717</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.5516363870635246</v>
+        <v>-0.2050943611742184</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.5222607693885806</v>
+        <v>-0.1766403179144831</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.01213</t>
+          <t>X &gt; -0.01196</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1413</v>
+        <v>3666</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1.032654768647568</v>
+        <v>-0.02100844695185344</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.7997163660494806</v>
+        <v>0.06776737069220218</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.8282774406808358</v>
+        <v>-0.1219020642411763</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.8173873128790206</v>
+        <v>0.1319261727759411</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1.266968920672063</v>
+        <v>-0.01058417636395603</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.4741389781920304</v>
+        <v>-0.07932763346227034</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.03629791628699053</v>
+        <v>-0.1219693196397458</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.4308854824945101</v>
+        <v>-0.1384496450910078</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.442605058840719</v>
+        <v>-0.5385734814704506</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.3927821236225171</v>
+        <v>-0.3654209558476254</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.6120570678561847</v>
+        <v>-0.3096438304097404</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.3741464372001175</v>
+        <v>-0.3963247562517935</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.6133183356881489</v>
+        <v>-0.3649255026402614</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.3441170800983926</v>
+        <v>-0.4238909456486653</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.01046</t>
+          <t>X &gt; -0.0103</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1359</v>
+        <v>3524</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.8789956973853279</v>
+        <v>-0.03534068419565273</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.140769431462594</v>
+        <v>-0.1045455625122145</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.8926358679327677</v>
+        <v>-0.2011592226389354</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.096256572073663</v>
+        <v>0.08590964315818184</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.364878643868693</v>
+        <v>-0.2105337287861104</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.4554725106343511</v>
+        <v>-0.350678271011418</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.2166327191195663</v>
+        <v>-0.504987359924371</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.4635518007204524</v>
+        <v>-0.2768216448194423</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.513016806594273</v>
+        <v>-0.803977640603641</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.2084965094799429</v>
+        <v>-0.6464116445845249</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.3711201138912301</v>
+        <v>-0.5518744041490677</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.6557838446383357</v>
+        <v>-0.7569423463489784</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.9615511595610826</v>
+        <v>-0.6790864976755344</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.3183394148049814</v>
+        <v>-0.692859465154541</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.008795</t>
+          <t>X &gt; -0.008652</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1294</v>
+        <v>3376</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.5473622956483766</v>
+        <v>-0.4006563669167633</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.9797338295376292</v>
+        <v>-0.1074504116737458</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.5848651229410393</v>
+        <v>-0.3091350967795563</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.7921598580138749</v>
+        <v>-0.04477594893496928</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.024154667595013</v>
+        <v>-0.3306838558221443</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.2082058600445436</v>
+        <v>-0.4308972215588014</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.5704368780450011</v>
+        <v>-0.5882748386828851</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.8834182722004371</v>
+        <v>-0.4775510521299395</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-2.059943539842337</v>
+        <v>-0.9364415813710991</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.3637724285739594</v>
+        <v>-0.9419006488647383</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.02840229610141876</v>
+        <v>-0.8047496783308361</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.9544438491806986</v>
+        <v>-0.9315733627652989</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.100131554955908</v>
+        <v>-0.8615557252622352</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.07761269563171425</v>
+        <v>-1.063607645539811</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.007129</t>
+          <t>X &gt; -0.007</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1206</v>
+        <v>3183</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.3554468986174371</v>
+        <v>-0.4471237902339738</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.101599637073697</v>
+        <v>-0.132790699498031</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.5414416742787651</v>
+        <v>-0.2915071965185305</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.6716948068862649</v>
+        <v>-0.1443088721247108</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.9597198728058345</v>
+        <v>-0.5089730055798469</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.1027490508556426</v>
+        <v>-0.5079368120737868</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.9318996415770613</v>
+        <v>-0.7637789496859853</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.233657068480973</v>
+        <v>-0.7122152650632643</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-2.905642992053927</v>
+        <v>-1.132533328855104</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.106761554565296</v>
+        <v>-1.243802049339671</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.9803890510683004</v>
+        <v>-1.305748517770994</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-2.14294208821746</v>
+        <v>-1.411100601998207</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-2.020824330132065</v>
+        <v>-1.123079512394511</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.024834341139361</v>
+        <v>-1.28831852814632</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.005462</t>
+          <t>X &gt; -0.005347</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1126</v>
+        <v>2946</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.556959557774114</v>
+        <v>-0.368715962943952</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.470209305763824</v>
+        <v>-0.001500365653626545</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.075340599167234</v>
+        <v>-0.276525182347136</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.205593731774734</v>
+        <v>-0.2294494473088378</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.463632693693718</v>
+        <v>-0.3433304728520881</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.4823958726989517</v>
+        <v>-0.2644562375822659</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.4880774371331142</v>
+        <v>-0.6016782434279691</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.9552608359146149</v>
+        <v>-0.643922837077838</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-2.386644354131796</v>
+        <v>-1.093076657425001</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.7545000356136242</v>
+        <v>-1.34837943735134</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.515990948583692</v>
+        <v>-1.29715931232677</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.851827479483582</v>
+        <v>-1.345899278801141</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.868536627143158</v>
+        <v>-1.204501212002157</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.7307158277265557</v>
+        <v>-1.401221021215086</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.003796</t>
+          <t>X &gt; -0.003695</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1035</v>
+        <v>2718</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.2495838164598965</v>
+        <v>-0.4838475072657573</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>2.157030456035791</v>
+        <v>0.1234403983959496</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.762161749439201</v>
+        <v>-0.1047686311988372</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.796075768366542</v>
+        <v>-0.1013292158286916</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.835689235375291</v>
+        <v>-0.2160388352917408</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.7413700717964673</v>
+        <v>-0.1555668250830351</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.6934118614835256</v>
+        <v>-0.7344226132646838</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.064163244835903</v>
+        <v>-0.9979835966420794</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-2.475211347025919</v>
+        <v>-1.205916524656409</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.107400177184033</v>
+        <v>-1.504769927892944</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.5406973780686357</v>
+        <v>-1.432162936974073</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-2.09343998817684</v>
+        <v>-1.524684497094697</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.785046696560791</v>
+        <v>-1.262707405445639</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.569141789405279</v>
+        <v>-1.347719359966014</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.00213</t>
+          <t>X &gt; -0.002042</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>951</v>
+        <v>2466</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.3468414615712376</v>
+        <v>-0.5632737212893062</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>2.184296242926393</v>
+        <v>0.4717104773711256</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.89424933926481</v>
+        <v>0.05858103710131957</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.919680668937303</v>
+        <v>0.1300129125188931</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>2.115012074410203</v>
+        <v>-0.02231357495720232</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.8983124179985253</v>
+        <v>-0.02636647722223273</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.6554664199453129</v>
+        <v>-0.8174421956907381</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.9127862300594458</v>
+        <v>-1.222217385205504</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2.128035853912259</v>
+        <v>-1.404657031606817</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-1.40418412393494</v>
+        <v>-1.809231698382021</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.7694830935830623</v>
+        <v>-1.546435484367706</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-2.042338466487081</v>
+        <v>-1.611442052629073</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.66953137325504</v>
+        <v>-1.563567318266195</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.3682853301480549</v>
+        <v>-1.477699003649924</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -0.0004641</t>
+          <t>X &gt; -0.00039</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>852</v>
+        <v>2191</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.7411018716118392</v>
+        <v>-0.1194264755843051</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>2.152298008346243</v>
+        <v>1.155512596983371</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.874388366077135</v>
+        <v>0.7403992189195066</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2.238559627339598</v>
+        <v>0.8047886520609708</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.934056540922398</v>
+        <v>0.291595294150369</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.7758100773068648</v>
+        <v>0.4320219105911036</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.9482679022604898</v>
+        <v>-0.538376251134622</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.712875188629809</v>
+        <v>-0.7529875382032074</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.710643224695019</v>
+        <v>-0.6772954350448828</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-1.272712203633951</v>
+        <v>-1.390539971693649</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.7748894155393629</v>
+        <v>-1.023377089902588</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-2.668403663961143</v>
+        <v>-1.191807160113399</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-2.556292529043617</v>
+        <v>-0.9937833967799463</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.193895140429305</v>
+        <v>-0.8795689997224798</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.001202</t>
+          <t>X &gt; 0.001262</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>768</v>
+        <v>1948</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.9390341751322495</v>
+        <v>-0.3358700652636628</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>2.574624902104624</v>
+        <v>1.452098182993538</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>3.087667998361468</v>
+        <v>1.290222606166211</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>2.180307641993615</v>
+        <v>0.6817148065906409</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>2.290394857531041</v>
+        <v>0.1715922766123228</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.7140685401554876</v>
+        <v>0.3435523432133465</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.2797560862076907</v>
+        <v>-0.7376021163440925</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.09758883563854681</v>
+        <v>-0.6923756781636214</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.067679630911755</v>
+        <v>-0.5996693100962318</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.7489736471085209</v>
+        <v>-1.039752040852314</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.4748444571453376</v>
+        <v>-0.4986712965992979</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.497595211577831</v>
+        <v>-0.9485155679845931</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.325732083034225</v>
+        <v>-0.6732933831851042</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.616697582575398</v>
+        <v>-0.7781648046628007</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.002868</t>
+          <t>X &gt; 0.002915</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>665</v>
+        <v>1676</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.6249779315702142</v>
+        <v>0.3974222483973975</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>2.930916210538342</v>
+        <v>2.143052270701112</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>3.284550497953724</v>
+        <v>2.138200763779871</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.666300636549252</v>
+        <v>1.350842717280322</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>2.576981217884267</v>
+        <v>0.845692659176926</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.011582121027402</v>
+        <v>1.11672182606025</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.3271482538300816</v>
+        <v>-0.006872222476751233</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.4596650049736226</v>
+        <v>0.1216517483880963</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.5008851060962414</v>
+        <v>0.06066959186532017</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.001684953792832289</v>
+        <v>-0.5510121586039176</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.74258720914596</v>
+        <v>0.4096676316969905</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.2380131327499839</v>
+        <v>0.08647725008330553</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.2732963060918649</v>
+        <v>0.4751022131683058</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2.081688184079155</v>
+        <v>0.5559248681182964</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.004534</t>
+          <t>X &gt; 0.004567</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>567</v>
+        <v>1444</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.6545591608404564</v>
+        <v>0.3427754295207492</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>3.26340911945735</v>
+        <v>2.144975753727799</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>3.219417605843212</v>
+        <v>1.92691959509505</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>2.647916352485801</v>
+        <v>1.405946528264813</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>2.811249523378542</v>
+        <v>0.9752278279957949</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.7496744105592583</v>
+        <v>0.9656703895907128</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.840687617715794</v>
+        <v>-0.1871151880172235</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.603732689936059</v>
+        <v>0.244847980090924</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.2147364405344661</v>
+        <v>-0.09275934932258423</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.6926076187258303</v>
+        <v>-0.8043655592070778</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>2.245323538696475</v>
+        <v>0.5123717334317561</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.2700653682862608</v>
+        <v>0.06265583322829826</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.05051713594427554</v>
+        <v>0.3735037499379104</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2.139239469700613</v>
+        <v>0.2232173928606258</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.0062</t>
+          <t>X &gt; 0.00622</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>470</v>
+        <v>1190</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.2735651701042627</v>
+        <v>0.5683738608608024</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>3.522106710893567</v>
+        <v>2.596861087104159</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>2.279780377178334</v>
+        <v>1.747436115077747</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>2.621897916565494</v>
+        <v>1.84100657660867</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>3.142798735391629</v>
+        <v>1.768934672248413</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>2.28960552970522</v>
+        <v>2.113845507747691</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.567929137273708</v>
+        <v>1.153158162248083</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2.162316863757596</v>
+        <v>1.10590479973758</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.1904889520975885</v>
+        <v>0.9609595869595609</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>1.675820242653529</v>
+        <v>-0.1408483781360488</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>4.231151844025966</v>
+        <v>1.081822419942974</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>1.293135850628296</v>
+        <v>0.9482744597878039</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.9953007183842146</v>
+        <v>1.199828056516367</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>4.010979497469016</v>
+        <v>1.558211224188177</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.007867</t>
+          <t>X &gt; 0.007872</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>381</v>
+        <v>956</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.31850359436141</v>
+        <v>-0.1940137436320697</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>3.22483099876294</v>
+        <v>2.411539915943962</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.568182187454305</v>
+        <v>1.971459824980116</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>2.436655215349766</v>
+        <v>1.430630050250784</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3.207134523837809</v>
+        <v>2.098799034122749</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.082306601306939</v>
+        <v>2.037754816058758</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>1.472638500832559</v>
+        <v>0.6524537859811659</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1.53038948525316</v>
+        <v>0.08078263173418065</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.6819880242677101</v>
+        <v>0.4382105170524042</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>2.194067563649227</v>
+        <v>-0.2025032583569484</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>4.089051772140046</v>
+        <v>1.057230729826372</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.9738286302728838</v>
+        <v>0.5685963298804424</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.291106827726928</v>
+        <v>1.194470581169547</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>3.165500076013714</v>
+        <v>1.211001210475565</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.009533</t>
+          <t>X &gt; 0.009525</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>302</v>
+        <v>745</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.01819079545749958</v>
+        <v>0.5939502796260783</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.193001311858886</v>
+        <v>1.463453431957376</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1.460384260891423</v>
+        <v>1.411249816043565</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1.590637393498923</v>
+        <v>1.348049621812322</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>3.038971145314171</v>
+        <v>1.615129196233411</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.6874064605132872</v>
+        <v>1.77827503794903</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>1.59605022668471</v>
+        <v>1.290880114924477</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.459992655717784</v>
+        <v>0.1526705315404229</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.2566363695373681</v>
+        <v>0.2259165629371083</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.879993412322122</v>
+        <v>-0.7582304213122129</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>3.324246710521102</v>
+        <v>1.318947615058462</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.04737158972083222</v>
+        <v>0.8164130157359324</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.3728830212240695</v>
+        <v>1.604315853697692</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>2.525844933568777</v>
+        <v>1.158910564326909</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.0112</t>
+          <t>X &gt; 0.01118</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>237</v>
+        <v>585</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-1.232934118529307</v>
+        <v>0.3299868655474185</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.09657311460883733</v>
+        <v>1.198000265480317</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>2.040203748414832</v>
+        <v>1.581502560022848</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.4826931679421591</v>
+        <v>0.686086677970188</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2.05397659422021</v>
+        <v>-0.02314304606567674</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-1.024108894224469</v>
+        <v>-0.06764935831093766</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.5789211015834184</v>
+        <v>0.3604607952434122</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.3102032254681291</v>
+        <v>-0.790368532304015</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.63702589646055</v>
+        <v>-1.193231030707132</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.04449448813177526</v>
+        <v>-2.385030168917332</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>2.371386733434449</v>
+        <v>-0.7093894468356439</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.391698463650506</v>
+        <v>-1.529712149181172</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.811953074595408</v>
+        <v>-0.2404612930928778</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>1.391354755571186</v>
+        <v>0.3271546990139953</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.01286</t>
+          <t>X &gt; 0.01283</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>186</v>
+        <v>457</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>1.807636948607225</v>
+        <v>2.104236807893599</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>2.346600970051583</v>
+        <v>0.8313114431414306</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>4.102269897863593</v>
+        <v>2.624723865826212</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.4690821702560299</v>
+        <v>0.129128440486781</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>2.61883299819462</v>
+        <v>0.02847564887905918</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.8471659243047824</v>
+        <v>-0.7682422252057748</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.469534050179213</v>
+        <v>-1.071770965215919</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.399083040358562</v>
+        <v>-1.320021228258682</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-2.53535174374516</v>
+        <v>-1.599821765525434</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.3779639314419754</v>
+        <v>-2.230922181111318</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>2.861382650135141</v>
+        <v>-0.4662579126756654</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.405309461336635</v>
+        <v>-1.08833490255229</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-1.825564072281537</v>
+        <v>-0.1955754714018028</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.5746948944033576</v>
+        <v>-0.8451133441511942</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.01453</t>
+          <t>X &gt; 0.01448</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>136</v>
+        <v>332</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-1.758144202562917</v>
+        <v>1.272837723219403</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>1.777341008002239</v>
+        <v>1.931994261943984</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3.58835465434683</v>
+        <v>3.043246973574497</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>2.983313669307265</v>
+        <v>1.667448020777307</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>3.18018657188216</v>
+        <v>0.2255440098502888</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.1988420786374832</v>
+        <v>0.2217132202082723</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-1.754164031203871</v>
+        <v>-0.1642019583350063</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-2.221347429985371</v>
+        <v>0.272343855709579</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-3.017641433814731</v>
+        <v>1.114976157018127</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.9265901482544265</v>
+        <v>-1.542171554974381</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>3.280421233310342</v>
+        <v>2.168789937367841</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-2.567548550520698</v>
+        <v>0.09473435478339809</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-1.517214926171476</v>
+        <v>1.180607597855527</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.532199476248131</v>
+        <v>-0.4008856675805887</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.0162</t>
+          <t>X &gt; 0.01613</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>105</v>
+        <v>249</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-2.96962879640045</v>
+        <v>0.3190839694656518</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.1807023525400524</v>
+        <v>0.1247653462813361</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.7382145983244186</v>
+        <v>0.1316003872291134</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.8684677309319184</v>
+        <v>-0.5413873205881501</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>1.282427468240698</v>
+        <v>-1.882889725089463</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-2.229654403567444</v>
+        <v>-2.790334972562817</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-3.266769073220686</v>
+        <v>-2.473438906126169</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-3.733952472002187</v>
+        <v>-2.137294698507283</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-5.699714262946387</v>
+        <v>-1.796670429327257</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-3.692696590831453</v>
+        <v>-4.654621354171177</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.08792610562522896</v>
+        <v>-1.244864681106066</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-6.720209614946462</v>
+        <v>-3.218518657264788</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-3.330940416367554</v>
+        <v>-1.229030956361335</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-2.128838131710317</v>
+        <v>-2.609721008946046</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.01786</t>
+          <t>X &gt; 0.01779</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>86</v>
+        <v>196</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>2.110920704159525</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>2.871732252872278</v>
+        <v>2.030346855993649</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.1512821509268463</v>
+        <v>-0.4052408552919928</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>3.769907376557612</v>
+        <v>0.7453924515616634</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>3.231486161485442</v>
+        <v>-0.8133052647993253</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.04055600617783739</v>
+        <v>-2.556747561694849</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.04417771109444146</v>
+        <v>-1.110845676063065</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.6514295877984821</v>
+        <v>-0.04730207495185113</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-4.060733089081488</v>
+        <v>-0.6184883131072709</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-1.422486181086171</v>
+        <v>-2.99901935433509</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>4.186713982968342</v>
+        <v>0.3677080588332871</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-5.081228441081564</v>
+        <v>-3.169342360239959</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-2.013110959003221</v>
+        <v>-1.548676887022765</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.6005989290525093</v>
+        <v>-1.322941236796233</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.01953</t>
+          <t>X &gt; 0.01944</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>68</v>
+        <v>160</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-5.434614790798214</v>
+        <v>1.89408396946564</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-2.634423697880116</v>
+        <v>2.157897876401819</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-4.499880639770822</v>
+        <v>-1.36187350835322</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-1.428451036575083</v>
+        <v>-1.856648364764858</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-1.966872251647253</v>
+        <v>-4.269937917860553</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-3.140018549225715</v>
+        <v>-5.222563888225466</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.283575795909762</v>
+        <v>-2.182274247491634</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.7507591946912626</v>
+        <v>-2.024342891278373</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-5.223523786755912</v>
+        <v>-1.460325047801149</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-1.661884265901492</v>
+        <v>-2.935243844131008</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>4.0157153509574</v>
+        <v>0.610054997608799</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-4.773430903461872</v>
+        <v>-2.480566850035878</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.7819208085244185</v>
+        <v>-1.025717703349287</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-4.943964182130486</v>
+        <v>-2.049982053122761</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.0212</t>
+          <t>X &gt; 0.02109</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>55</v>
+        <v>129</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-1.584347411119069</v>
+        <v>4.883425054736968</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>2.258624430462127</v>
+        <v>4.822626558572367</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1.863755723865538</v>
+        <v>2.102273778468486</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.1758270382912173</v>
+        <v>-0.09308247329199304</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-3.998957813144585</v>
+        <v>-4.507341018635749</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-3.701515875428925</v>
+        <v>-5.76035458589989</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.1498859563375703</v>
+        <v>-2.744289751367603</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-2.435251173300891</v>
+        <v>-3.986552193603949</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-7.950796514028639</v>
+        <v>-2.497146753227497</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-3.34637624451112</v>
+        <v>-4.122259348006978</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>3.721597703898581</v>
+        <v>0.3242022844305055</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-7.153110047846894</v>
+        <v>-3.517388555462226</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-2.11881920424635</v>
+        <v>-1.611958013426808</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-5.505461508333696</v>
+        <v>-2.936609960099503</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 0.02286</t>
+          <t>X &gt; 0.02274</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>44</v>
+        <v>106</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-4.766165592937249</v>
+        <v>4.122857554371308</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>2.713169885007588</v>
+        <v>5.341860140552761</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>2.318301178410998</v>
+        <v>2.11690007655244</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.1758270382912173</v>
+        <v>-0.5830634591044799</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-4.908048722235492</v>
+        <v>-7.725126597105834</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-2.337879511792558</v>
+        <v>-7.427752567470748</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.1498859563375703</v>
+        <v>-4.682274247491634</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-2.889796627846337</v>
+        <v>-7.979531570523655</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-12.04170560493773</v>
+        <v>-7.097117500631335</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-6.07364897178384</v>
+        <v>-7.947036296961194</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>2.812506794807675</v>
+        <v>-2.491360096730823</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-8.516746411483261</v>
+        <v>-7.173963076450974</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-4.391546476973616</v>
+        <v>-5.70732147693419</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-6.414552417424602</v>
+        <v>-6.424982053122754</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.02453</t>
+          <t>X &gt; 0.0244</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>33</v>
+        <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.9782868050584597</v>
+        <v>9.423845874227553</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>3.470745642583346</v>
+        <v>11.3840883525923</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.04557390568371744</v>
+        <v>3.846459824980116</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>3.206130068594256</v>
+        <v>3.976684968568478</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.3625941767809522</v>
+        <v>-3.704461727384363</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.06515223906529144</v>
+        <v>-2.216611507273079</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.1498859563375703</v>
+        <v>-1.110845676063065</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.6170693551190709</v>
+        <v>-3.958866700802183</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-12.79928136251349</v>
+        <v>-5.210325047801149</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-7.588800486935355</v>
+        <v>-7.250720034607198</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>4.32765830995919</v>
+        <v>-0.3125640500102449</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-4.728867623604472</v>
+        <v>-3.849614469083491</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.9114838260566884</v>
+        <v>-3.079289131920717</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-1.869097871970062</v>
+        <v>-2.853553481694185</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that DXY Ret-10 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that DXY Ret-10 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3904,1561 +3904,1561 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.02379</t>
+          <t>X &lt; -0.02352</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>33</v>
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>5.082319255547603</v>
+        <v>-1.290439840058163</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.4404426122803073</v>
+        <v>3.050755019258958</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.04557390568371744</v>
+        <v>2.655983634503919</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>3.206130068594256</v>
+        <v>-3.166172174288668</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-3.392897207083976</v>
+        <v>-2.513985536908166</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-3.095455269368315</v>
+        <v>0.1643408736793006</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>2.880417073965468</v>
+        <v>0.0796305144131324</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>2.413233675183967</v>
+        <v>1.993514251578766</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>5.382536819304697</v>
+        <v>5.503960666484559</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>7.562714664579794</v>
+        <v>7.034994251107086</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>7.357961340262214</v>
+        <v>9.211245473799281</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>7.392344497607645</v>
+        <v>6.864671245202217</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>10.00239291696577</v>
+        <v>7.634996582365005</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>7.221811218939031</v>
+        <v>5.479779851639151</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.02212</t>
+          <t>X &lt; -0.02187</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>53</v>
+        <v>110</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>2.223542811865492</v>
+        <v>1.155447605829288</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-1.27482325392895</v>
+        <v>0.4533524218563585</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-1.66969196052554</v>
+        <v>3.69494467346496</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>2.234146077742338</v>
+        <v>0.1888061806896815</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-2.07786004299021</v>
+        <v>1.468698445775807</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-1.780418105274549</v>
+        <v>1.766072475410894</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>1.90843308311355</v>
+        <v>1.681362116144726</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>8.988419495652799</v>
+        <v>6.66883892690344</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>5.153834703810126</v>
+        <v>5.698765861289765</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>8.07729442444257</v>
+        <v>7.576119792232625</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>7.872541100124991</v>
+        <v>9.189600452154252</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>7.906924257470422</v>
+        <v>7.405796786327755</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>7.48666964652552</v>
+        <v>6.985645933014347</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>7.736390978801808</v>
+        <v>7.211381583240879</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.02046</t>
+          <t>X &lt; -0.02022</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>63</v>
+        <v>137</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1.474815648043993</v>
+        <v>1.53368250961163</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-3.311361139523441</v>
+        <v>0.6524234238470754</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-6.880833020723209</v>
+        <v>1.71750605369057</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-3.575976713512532</v>
+        <v>-1.071976831918143</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-7.289001103187879</v>
+        <v>-1.610266385013837</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-6.991559165472218</v>
+        <v>-2.042819362678017</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.8602150537634472</v>
+        <v>0.06225129995362266</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>6.742238004188295</v>
+        <v>5.434598714561048</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>5.093936530704404</v>
+        <v>5.373616558038272</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>4.243811345676477</v>
+        <v>5.253624769007679</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>5.626359608660486</v>
+        <v>6.508777625346028</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>5.660742766005917</v>
+        <v>5.813228770402084</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>3.653186567759427</v>
+        <v>4.663150909789401</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>5.490209487337303</v>
+        <v>4.158959552716667</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.01879</t>
+          <t>X &lt; -0.01857</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>77</v>
+        <v>178</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.5453863721580348</v>
+        <v>2.013465991937558</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-3.455661283823588</v>
+        <v>-0.7213156067442483</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-3.850529990420178</v>
+        <v>2.254699525354653</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-3.720276857812678</v>
+        <v>-0.9858618479109253</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-5.557399371586143</v>
+        <v>-2.085949153815612</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-6.558658732571779</v>
+        <v>-2.350372876989503</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-1.448587255038866</v>
+        <v>-0.1878922250197235</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1.980333242283528</v>
+        <v>2.154027895238478</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>3.21803465480253</v>
+        <v>3.778438997142672</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>1.069208171073299</v>
+        <v>2.36672244800382</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.86445484675572</v>
+        <v>3.285616795361612</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.898838004101151</v>
+        <v>2.196399442098951</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>1.777284691857552</v>
+        <v>3.461641847212512</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>3.325707322835136</v>
+        <v>2.563781991821067</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.01713</t>
+          <t>X &lt; -0.01691</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>98</v>
+        <v>231</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.4526219936793581</v>
+        <v>2.064538514920187</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.02337928011300505</v>
+        <v>1.752053720557662</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-4.499880639770822</v>
+        <v>3.52178450030479</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-3.349219343898014</v>
+        <v>-0.2440942522107434</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-5.9284568855008</v>
+        <v>-1.648184671107309</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-5.63101494778514</v>
+        <v>-0.917910208571783</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.4067003145344117</v>
+        <v>-0.1368197020370943</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.06048308424708893</v>
+        <v>1.127713385777909</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.8989251928359181</v>
+        <v>3.664133826657732</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-1.992016318722612</v>
+        <v>1.515513731626569</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.1559533165095885</v>
+        <v>2.60951387206768</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-2.162386485694761</v>
+        <v>1.3451907257217</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.5418247701090593</v>
+        <v>2.223741171109594</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.7283047254325368</v>
+        <v>1.150775522634824</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.01546</t>
+          <t>X &lt; -0.01526</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>122</v>
+        <v>306</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-1.673766189062434</v>
+        <v>0.4602604400538866</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.8263234085840665</v>
+        <v>0.4830612750946273</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-5.319552770918364</v>
+        <v>2.049074204065079</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-3.549955376015781</v>
+        <v>0.2185150339279502</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-4.908048722235492</v>
+        <v>-0.3197745191677441</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-4.610606784519831</v>
+        <v>0.3043968960882637</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.2226922850931388</v>
+        <v>1.526876079305751</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1.394853148606714</v>
+        <v>1.71340220676084</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2.153525393571954</v>
+        <v>4.593596520826303</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.155616184898591</v>
+        <v>2.763285567633702</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.098646884226447</v>
+        <v>3.538976566236251</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.325986351870739</v>
+        <v>2.592962561728832</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.106896700520565</v>
+        <v>2.826406479657251</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.9624967629032639</v>
+        <v>1.744952587400128</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.01379</t>
+          <t>X &lt; -0.01361</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>150</v>
+        <v>399</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-0.3505902159980181</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-1.438345266507568</v>
+        <v>-0.708643476981635</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-5.166547306437486</v>
+        <v>0.6509711031755998</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-4.369627507163322</v>
+        <v>-0.2213100189001977</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-4.908048722235492</v>
+        <v>-0.5089730055798469</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-3.94394011785316</v>
+        <v>-0.2115989759447601</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.304659498207897</v>
+        <v>0.9568234968692622</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.8374760994263966</v>
+        <v>1.241634552330652</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1.443142879910752</v>
+        <v>4.438797759216392</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.406982305117175</v>
+        <v>3.338252396470494</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.611735629434754</v>
+        <v>2.632298105378226</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-2.244019138755988</v>
+        <v>3.418555956981663</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-1.997607083034225</v>
+        <v>3.499658236500338</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.2521142492420623</v>
+        <v>3.224140753894787</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.01213</t>
+          <t>X &lt; -0.01196</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>193</v>
+        <v>502</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.1618321025934009</v>
+        <v>0.1087254037285916</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.7371362855058408</v>
+        <v>0.2903679959237309</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-3.722678567231959</v>
+        <v>1.290018921925657</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-3.074290719598551</v>
+        <v>-0.3725846197449414</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-2.058307789593009</v>
+        <v>0.6827513251673309</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.724596421825531</v>
+        <v>1.378531729304413</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>2.817612866083543</v>
+        <v>1.891430931791241</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>2.868564182327937</v>
+        <v>2.021971849757492</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>3.325699011171544</v>
+        <v>5.148240689250649</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.9211696810659049</v>
+        <v>3.899915518418794</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.3198530733034914</v>
+        <v>3.496011172907608</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.2854699159580605</v>
+        <v>4.12799888701592</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.223859241928871</v>
+        <v>3.907051220953505</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>1.616535665476945</v>
+        <v>4.331990058431032</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.01046</t>
+          <t>X &lt; -0.0103</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>247</v>
+        <v>644</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.9478572263487308</v>
+        <v>0.1588355222606808</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-2.283149584996096</v>
+        <v>1.187400981991885</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-3.082876591187826</v>
+        <v>1.413747609659197</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-3.762340057770608</v>
+        <v>-0.008822277808341994</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-1.871611475271926</v>
+        <v>1.626801212574229</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.3595946387708437</v>
+        <v>2.545293254631673</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>3.604254639908291</v>
+        <v>3.547539417104645</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>2.327354641936509</v>
+        <v>2.304073257789952</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>2.671213055349355</v>
+        <v>5.34868116337897</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>1.821087870321428</v>
+        <v>4.49876236704911</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>1.211476246408701</v>
+        <v>3.983502202577746</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>1.245859403754132</v>
+        <v>5.104836876672195</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.82560479280923</v>
+        <v>4.684686023358786</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>1.480184424680665</v>
+        <v>4.755142170479729</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.008795</t>
+          <t>X &lt; -0.008652</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>312</v>
+        <v>792</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>2.314253987482338</v>
+        <v>1.685750636132312</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.8998837280460279</v>
+        <v>0.9584029269068708</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.9742396141298002</v>
+        <v>1.573732552252835</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.485012122547936</v>
+        <v>0.5675940594775639</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.2201564059696395</v>
+        <v>1.796981274058638</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.8381111641981178</v>
+        <v>2.346880556218977</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>4.279018472566868</v>
+        <v>3.146008580791197</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>3.491322253272543</v>
+        <v>2.678939937004458</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>4.071348008115883</v>
+        <v>4.764422426946318</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>3.862248464113591</v>
+        <v>4.798342014454846</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>2.695956678257559</v>
+        <v>4.214852977406778</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>2.089314194577348</v>
+        <v>4.754281634812607</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>1.028033942606797</v>
+        <v>4.460393407761828</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>2.880319377447194</v>
+        <v>5.317442189301488</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.007129</t>
+          <t>X &lt; -0.007</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>400</v>
+        <v>985</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>2.506561679790032</v>
+        <v>1.427713411090018</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.8550119331742323</v>
+        <v>0.8317557444221251</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.4998806397708222</v>
+        <v>1.14764425814424</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.6196275071633224</v>
+        <v>0.7702551885346338</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.5919512777645153</v>
+        <v>1.957853960312043</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.639393215480169</v>
+        <v>2.052182304667937</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>4.30465949820789</v>
+        <v>2.982700371797712</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>3.587476099426389</v>
+        <v>2.820200255929755</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>5.276476213244088</v>
+        <v>4.282060739000876</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>5.176351028216168</v>
+        <v>4.650416054346152</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>4.971597703898588</v>
+        <v>4.851806266644331</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>5.005980861244019</v>
+        <v>5.19075294691843</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>3.335726250299111</v>
+        <v>4.262987880407067</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>5.085447582575398</v>
+        <v>4.793292058552375</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.005462</t>
+          <t>X &lt; -0.005347</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>480</v>
+        <v>1222</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.673228346456689</v>
+        <v>0.8742394522806975</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-1.396678599840897</v>
+        <v>0.3268831464509248</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.583213973104158</v>
+        <v>0.8322754278169953</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.661294173829987</v>
+        <v>0.7988344502924321</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.5330487222354989</v>
+        <v>1.078875502761377</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.02727345118650248</v>
+        <v>0.9670842296141444</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.387992831541219</v>
+        <v>1.864370597025548</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>2.129142766093054</v>
+        <v>1.970133377134069</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>2.693142879910759</v>
+        <v>3.136647128958266</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>3.30135102821616</v>
+        <v>3.759723422644768</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>2.888264370565246</v>
+        <v>3.636855324941045</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>3.130980861244012</v>
+        <v>3.753066537852824</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>2.085726250299111</v>
+        <v>3.414748745095885</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>3.377114249242062</v>
+        <v>3.885983576991812</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.003796</t>
+          <t>X &lt; -0.003695</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>571</v>
+        <v>1450</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>2.052016225244564</v>
+        <v>0.8937396168485634</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-2.181935010097305</v>
+        <v>0.04012928136049254</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-2.401978541868729</v>
+        <v>0.3340631307652373</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-2.271725409261229</v>
+        <v>0.3954177509376251</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.8870697012564719</v>
+        <v>0.6147039554176814</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.4148025887156308</v>
+        <v>0.5677253679728835</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2.297666491214876</v>
+        <v>1.722684430194313</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.830483092433376</v>
+        <v>2.219803114231269</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2.044427176466499</v>
+        <v>2.680784531799127</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>3.295878173575183</v>
+        <v>3.250100983455198</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>2.390599455212069</v>
+        <v>3.114365342436386</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>2.775245309580264</v>
+        <v>3.286674529274471</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.304202607567063</v>
+        <v>2.797558158719681</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>2.429580682400264</v>
+        <v>2.954328291704833</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.00213</t>
+          <t>X &lt; -0.002042</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>655</v>
+        <v>1702</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>2.689488509058322</v>
+        <v>0.8054689459914712</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.665987542930331</v>
+        <v>-0.4536044710160212</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-2.060856249526921</v>
+        <v>0.03190583436978045</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.930603116919421</v>
+        <v>-0.01392536007001866</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.9446340880891455</v>
+        <v>0.2106958849563441</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.4947531259832445</v>
+        <v>0.2733281305538711</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.859537546988378</v>
+        <v>1.479697583494278</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.23991512381663</v>
+        <v>2.068966967876555</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.9596823201143181</v>
+        <v>2.393902785434321</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>3.162992249590204</v>
+        <v>2.987934769264996</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>2.347551902371869</v>
+        <v>2.606970391263324</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.076591548266912</v>
+        <v>2.700102950199138</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.7403064029708659</v>
+        <v>2.632478536368694</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.75338651387311</v>
+        <v>2.505687747112262</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -0.0004641</t>
+          <t>X &lt; -0.00039</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>754</v>
+        <v>1977</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>2.738349759260224</v>
+        <v>0.1214083757314341</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.124879482843106</v>
+        <v>-1.085533149368771</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.519748189439696</v>
+        <v>-0.722345969192034</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.786846050209682</v>
+        <v>-0.7437125385900245</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.3385122983944342</v>
+        <v>-0.170329529785775</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.1735206918045975</v>
+        <v>-0.2772000681142899</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.860950888936365</v>
+        <v>0.8508232765103827</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.7315158345257231</v>
+        <v>1.091182626659986</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.08151600104249468</v>
+        <v>1.058633496182679</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>2.414414688693611</v>
+        <v>1.855790551417805</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.944409374986122</v>
+        <v>1.448762635443899</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>2.244044521721463</v>
+        <v>1.634885856084502</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.425911926691683</v>
+        <v>1.417061760484806</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.277755274883084</v>
+        <v>1.288725584712346</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.001202</t>
+          <t>X &lt; 0.001262</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>838</v>
+        <v>2220</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>2.572115911017676</v>
+        <v>0.2856156833657835</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.184868905760645</v>
+        <v>-1.100649132145186</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-2.294874680295251</v>
+        <v>-1.045577961794514</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.330294968426728</v>
+        <v>-0.4655102631004411</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.438442047622857</v>
+        <v>-0.01414619496357261</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.02181059858418877</v>
+        <v>-0.1216304649236193</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.9661612860505642</v>
+        <v>0.8732813080639232</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.02221984197704785</v>
+        <v>0.8362556685776141</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.6889175815053079</v>
+        <v>0.8004808954676434</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.563582531796115</v>
+        <v>1.192008408121247</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.5235070117744769</v>
+        <v>0.7170369795907732</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.6772219113633469</v>
+        <v>1.111775492306471</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.1010279263118719</v>
+        <v>0.871804819173235</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.3873568904512936</v>
+        <v>0.9624053342646377</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.002868</t>
+          <t>X &lt; 0.002915</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>941</v>
+        <v>2492</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.965160405904676</v>
+        <v>-0.2773903895087173</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.026455669904593</v>
+        <v>-1.287614944110999</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.845952826607338</v>
+        <v>-1.36187350835322</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.291071243893683</v>
+        <v>-0.7909432365597269</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.3432928835943017</v>
+        <v>-0.4478225332451657</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.1520080584051797</v>
+        <v>-0.5911536318152102</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.4002008994817743</v>
+        <v>0.2055462653288842</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.3854538368793428</v>
+        <v>0.1211981908859556</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.132131650730408</v>
+        <v>0.2026661310280389</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.7807612301290234</v>
+        <v>0.6184565168798173</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.3804214246880306</v>
+        <v>-0.02748010066636652</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.4523081929536446</v>
+        <v>0.1899788963525637</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.9788327295096053</v>
+        <v>-0.06965831330114014</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.6228414716222588</v>
+        <v>-0.1248215394790932</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.004534</t>
+          <t>X &lt; 0.004567</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1039</v>
+        <v>2724</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.737330910559251</v>
+        <v>-0.1906998341254038</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.8357811639434658</v>
+        <v>-0.9957298260532923</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.326803716693902</v>
+        <v>-0.9507797010978152</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.9080890456248625</v>
+        <v>-0.6373372617967448</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.1965102606970248</v>
+        <v>-0.4061141728990307</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.1009316770186359</v>
+        <v>-0.3652443572617443</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.1123518059002038</v>
+        <v>0.2829144663229499</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.9317546698043842</v>
+        <v>0.05593570109699186</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.229298570201529</v>
+        <v>0.2718898403543335</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.3267360137792039</v>
+        <v>0.6528889511734661</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.4554956551004636</v>
+        <v>-0.04476151615267554</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.7098516700360662</v>
+        <v>0.1938090677321114</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.033859890220626</v>
+        <v>0.03063325112941584</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.3991529949029484</v>
+        <v>0.1095260232355386</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.0062</t>
+          <t>X &lt; 0.00622</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1136</v>
+        <v>2978</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.372994017224123</v>
+        <v>-0.2356077195423936</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.5900734445977847</v>
+        <v>-0.9084560109976465</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.5455748401223133</v>
+        <v>-0.632986108889412</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.5910686319436351</v>
+        <v>-0.6368092226737048</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.07500830044286744</v>
+        <v>-0.6053936819356167</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.4805540604425076</v>
+        <v>-0.7101644244184939</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.1259204666427252</v>
+        <v>-0.2921938185372071</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.9445977142818691</v>
+        <v>-0.2717029315063328</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.309715519385634</v>
+        <v>-0.1801439612820346</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.04902276246105686</v>
+        <v>0.2631375715013249</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.045332815010831</v>
+        <v>-0.2246765460153597</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.050357166925004</v>
+        <v>-0.1714866217713649</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.382583608855818</v>
+        <v>-0.2705968168482826</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.9568059385513621</v>
+        <v>-0.4142365863665347</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.007867</t>
+          <t>X &lt; 0.007872</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1225</v>
+        <v>3212</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.57822291757504</v>
+        <v>0.05092615648024434</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.1962171449006149</v>
+        <v>-0.5972279390688158</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.4282194019858068</v>
+        <v>-0.5260160992199516</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.2979662693783069</v>
+        <v>-0.3336598590177289</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.1408112126179333</v>
+        <v>-0.5302283807372206</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.2132126477120124</v>
+        <v>-0.4813787375575629</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.02778653403851195</v>
+        <v>-0.03797477560595297</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.5208300894986877</v>
+        <v>0.1334414468198304</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.352293142909133</v>
+        <v>0.05855900566481154</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.08342892288408876</v>
+        <v>0.251945210595359</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.6141806172098185</v>
+        <v>-0.1218656866835772</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.7790925482176547</v>
+        <v>0.02332238456275348</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.9908043619457843</v>
+        <v>-0.1614553317339755</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.3329197643633819</v>
+        <v>-0.1671987405449187</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.009533</t>
+          <t>X &lt; 0.009525</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1304</v>
+        <v>3423</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.099833851043847</v>
+        <v>-0.1360281773447269</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.4821440301285165</v>
+        <v>-0.2033750627184858</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.01082272414355145</v>
+        <v>-0.2485979476191673</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.06462325736266905</v>
+        <v>-0.2057599289943965</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.3671806355626686</v>
+        <v>-0.2620707849934192</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.2478476913791781</v>
+        <v>-0.2693796853691524</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.0866028799982459</v>
+        <v>-0.1341692912234151</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.3805805187832547</v>
+        <v>0.114582451387129</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.012191474351617</v>
+        <v>0.1280646838207886</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.3582040144336176</v>
+        <v>0.3447751228955482</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.152828023513365</v>
+        <v>-0.1061592464075503</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.4585785257291732</v>
+        <v>0.003009792299891956</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.7593657742407629</v>
+        <v>-0.1670728435361966</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.02716537398643482</v>
+        <v>-0.07090668064247296</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.0112</t>
+          <t>X &lt; 0.01118</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1369</v>
+        <v>3583</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.257472094939338</v>
+        <v>-0.06021486191999514</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.7383966611447761</v>
+        <v>-0.08542432727097093</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.0206381051750526</v>
+        <v>-0.2019541983921798</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.3281146632663976</v>
+        <v>-0.02878863751742955</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.6636919915299799</v>
+        <v>0.08835829594791278</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.5643203291827916</v>
+        <v>0.122569779276624</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.3338140171583319</v>
+        <v>0.08095695027995475</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.01240321312901216</v>
+        <v>0.2699939713574508</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.737746981504273</v>
+        <v>0.3638109611174656</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.5273721806596399</v>
+        <v>0.5608880209372913</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.1767399358460651</v>
+        <v>0.2883176858408092</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.1856249781720436</v>
+        <v>0.4221528152360889</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.4918851448798591</v>
+        <v>0.2131215823650052</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.3422043393321559</v>
+        <v>0.1198128115158141</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.01286</t>
+          <t>X &lt; 0.01283</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1420</v>
+        <v>3711</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.7697195745268672</v>
+        <v>-0.2649611554336317</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.3893700892976781</v>
+        <v>0.004056887951648491</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.2161727746022848</v>
+        <v>-0.2687112300082504</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.3354286726119611</v>
+        <v>0.06420624421122056</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.6397040867532695</v>
+        <v>0.07818036170933595</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.4842632084527665</v>
+        <v>0.2021134443908252</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.6103516977862498</v>
+        <v>0.266623009097934</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.1431682990047491</v>
+        <v>0.298598997341486</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.6524970638304595</v>
+        <v>0.3601808725433102</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.466435416401815</v>
+        <v>0.4404291033790813</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.1913586040392232</v>
+        <v>0.2240156868925922</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.2271296243295282</v>
+        <v>0.300540071590838</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.5375131863206022</v>
+        <v>0.1919547104438166</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.4868560332796221</v>
+        <v>0.2713262195800255</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.01453</t>
+          <t>X &lt; 0.01448</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1470</v>
+        <v>3836</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1.133680323857817</v>
+        <v>-0.1160511656694823</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.5082852174363524</v>
+        <v>-0.06403559553164939</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.02226869947231336</v>
+        <v>-0.2108142413919438</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.1079844331351865</v>
+        <v>-0.06647675790058116</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.6550449005596235</v>
+        <v>0.05954842804322169</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.3792099160911633</v>
+        <v>0.08505838024488099</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.5660308491922805</v>
+        <v>0.1446838581549912</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.1667361130041201</v>
+        <v>0.1083354012775857</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.6718933519733099</v>
+        <v>0.06173951871797811</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.5839597238683325</v>
+        <v>0.2939228225356629</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.2433368343333626</v>
+        <v>-0.02634119931748558</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.159722741747153</v>
+        <v>0.1529662401152407</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.6098519809934047</v>
+        <v>0.06025441028115353</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.5922503036638318</v>
+        <v>0.1964986559491919</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.0162</t>
+          <t>X &lt; 0.01613</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1501</v>
+        <v>3919</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>1.158620112724947</v>
+        <v>-0.02606993539316704</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.6458186316098136</v>
+        <v>0.09258370697928342</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.2509499250132237</v>
+        <v>0.04238857816077513</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.3147578748964719</v>
+        <v>0.1101370768233352</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.8394595834123493</v>
+        <v>0.1967117766404698</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.5090740665440023</v>
+        <v>0.2789321647411711</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.6238084343781054</v>
+        <v>0.2846131697269101</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.2231143972987297</v>
+        <v>0.2646698475751279</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.5329050242808577</v>
+        <v>0.2687779083660331</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.7460449736586128</v>
+        <v>0.4526289572964757</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.5412916493410336</v>
+        <v>0.2368398012803965</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.08088099439981278</v>
+        <v>0.3621390923257621</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.5017154552305314</v>
+        <v>0.2370373986915268</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.680717402695322</v>
+        <v>0.3241886536902001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.01786</t>
+          <t>X &lt; 0.01779</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1520</v>
+        <v>3972</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1.080332171593298</v>
+        <v>-0.1095233078241904</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.4881639198441405</v>
+        <v>-0.0007366617507926776</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.2901456069483359</v>
+        <v>0.06999317505125191</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.1579315479547887</v>
+        <v>0.03812812945914601</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.7349958971870834</v>
+        <v>0.1163657746790037</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.3467142923022308</v>
+        <v>0.2265567147896164</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.3933003386543774</v>
+        <v>0.1807566647978902</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.0738830601271232</v>
+        <v>0.1296917995210265</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.6900152453630071</v>
+        <v>0.1831876502124317</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.5623562844579411</v>
+        <v>0.3029352303156685</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.2918999378013396</v>
+        <v>0.1375707208792392</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.09674760686906581</v>
+        <v>0.3119595717054438</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.6116421707535267</v>
+        <v>0.2332490723869327</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.5591317931017201</v>
+        <v>0.221543626635551</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.01953</t>
+          <t>X &lt; 0.01944</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1538</v>
+        <v>4008</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>1.168259670716793</v>
+        <v>-0.0810155082762023</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.7588012963977562</v>
+        <v>0.01237548834211566</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.4936342759230854</v>
+        <v>0.1038206941847264</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.4293348793477065</v>
+        <v>0.1480803559917305</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.9933779963118496</v>
+        <v>0.245714310170321</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.4834879591531092</v>
+        <v>0.3078145978303155</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.3987542418808303</v>
+        <v>0.2118727014498347</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.003536230229684634</v>
+        <v>0.2069102228222803</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.6780692413013725</v>
+        <v>0.2095603247380993</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.5497276515927823</v>
+        <v>0.2707631349318049</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.3449743272752031</v>
+        <v>0.1299689841458189</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.1686455195227197</v>
+        <v>0.2532236736548938</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.6824792113393841</v>
+        <v>0.1963763350642864</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.7375932262685083</v>
+        <v>0.2366945935838274</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.0212</t>
+          <t>X &lt; 0.02109</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1551</v>
+        <v>4039</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.9769986977848788</v>
+        <v>-0.1610739772273462</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.5573674880476318</v>
+        <v>-0.05606163976703016</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.2268074631230732</v>
+        <v>-0.01773770588408041</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.357060595730573</v>
+        <v>0.07654501631688504</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>1.040504332426885</v>
+        <v>0.2186984457758143</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.4730482991352503</v>
+        <v>0.2825942536079893</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.3883145818629714</v>
+        <v>0.211447947268617</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.04983131178160249</v>
+        <v>0.2523876402420271</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.6195315137359501</v>
+        <v>0.2298332113482005</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.5908713115387627</v>
+        <v>0.2840549438976794</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.3861179872211835</v>
+        <v>0.1427739486231516</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.1228851181374324</v>
+        <v>0.2653500022284163</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.6359049553746488</v>
+        <v>0.2057179402150666</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.7098834304155019</v>
+        <v>0.2474616210540219</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 0.02286</t>
+          <t>X &lt; 0.02274</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1562</v>
+        <v>4062</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>1.048361296892772</v>
+        <v>-0.1128178710251504</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.5565461766597437</v>
+        <v>-0.04202848589567765</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.2255344304718321</v>
+        <v>-0.006146771304365473</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.3557875630793319</v>
+        <v>0.08834181205242686</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>1.030648595772163</v>
+        <v>0.2757818070227671</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.4053676563747359</v>
+        <v>0.2918710012094223</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.3845317026807393</v>
+        <v>0.2452263669099324</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.0451438310557819</v>
+        <v>0.3324663515928208</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.5560046051702372</v>
+        <v>0.3343024417488891</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.6399060154284371</v>
+        <v>0.3588412517863588</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.4351526911108579</v>
+        <v>0.2172198192570178</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.133974353087396</v>
+        <v>0.3393150397279072</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.5823275269096015</v>
+        <v>0.3022726978321018</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.6917215902578562</v>
+        <v>0.3204635401810378</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.02453</t>
+          <t>X &lt; 0.0244</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1573</v>
+        <v>4084</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.9286149117291842</v>
+        <v>-0.1987583541857987</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.5557363230083894</v>
+        <v>-0.1370239985981812</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.2876906982126854</v>
+        <v>-0.03021905169876504</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.2911207490192993</v>
+        <v>-0.008822277808341994</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.8941072701551178</v>
+        <v>0.1502612025890002</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.3386317941603707</v>
+        <v>0.1433940785389467</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.3808016301875909</v>
+        <v>0.1453962487195639</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.02292999194417433</v>
+        <v>0.2051803361054922</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.6203491835813111</v>
+        <v>0.2555590314358369</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.6247637266288635</v>
+        <v>0.2998344337554855</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.4200104023112843</v>
+        <v>0.1578590103320678</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.2719733954268833</v>
+        <v>0.2305197872622102</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.7202178056449426</v>
+        <v>0.215867363970176</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.5466681801596351</v>
+        <v>0.2106692691103476</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/dxy/dxy_ret_10.xlsx
+++ b/workspaces/btc_daily_14days/dxy/dxy_ret_10.xlsx
@@ -568,1041 +568,1041 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.02269</t>
+          <t>X ≈ -0.02266</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>9.028688666340557</v>
+        <v>10.4196222416975</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-7.914750916950013</v>
+        <v>-5.927555609174021</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>7.032509323390798</v>
+        <v>8.453063086895689</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>11.00119653469334</v>
+        <v>12.27967548243173</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>14.30438552520305</v>
+        <v>15.48998364791239</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>6.927427154560746</v>
+        <v>8.373074547738554</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>6.844589100417913</v>
+        <v>8.31459872814758</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>21.74171020834776</v>
+        <v>22.6444039293519</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>6.320392606616871</v>
+        <v>7.816329310165628</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>9.315195687033992</v>
+        <v>10.69525757692328</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>9.112905382983584</v>
+        <v>10.49386129375382</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>9.149544203020035</v>
+        <v>10.55461096505798</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>4.886538564182459</v>
+        <v>6.459345025544941</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>12.80578717764997</v>
+        <v>14.11738707681427</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.02105</t>
+          <t>X ≈ -0.021</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>27</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>3.064637373141565</v>
+        <v>-0.6563013795145238</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1.45936146645024</v>
+        <v>-2.234583424394408</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-6.321613498925302</v>
+        <v>-6.321838642490093</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-6.192967846874126</v>
+        <v>-6.193527465723875</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-14.12258761095242</v>
+        <v>-14.07425562330852</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-17.52564442293777</v>
+        <v>-17.50184417076179</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-6.522663990338671</v>
+        <v>-6.474785697900259</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.4055259390551882</v>
+        <v>0.4546838799184698</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>4.043912226707533</v>
+        <v>4.117074931701829</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-4.20427299222559</v>
+        <v>-4.105047576480025</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-4.409883002122598</v>
+        <v>-4.310067034784801</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.674700503279702</v>
+        <v>-0.5510729368746183</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-4.797684532565427</v>
+        <v>-4.649038410434493</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-8.276833904974609</v>
+        <v>-8.104835145407947</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.01939</t>
+          <t>X ≈ -0.01936</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>3.604712686579205</v>
+        <v>3.292992922243521</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-5.295460767147354</v>
+        <v>-2.921462910687943</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>4.038553485629166</v>
+        <v>3.642430994918229</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.6960913304638225</v>
+        <v>-3.186136342963309</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-3.666861791125754</v>
+        <v>-5.99542382805145</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-3.370955106808594</v>
+        <v>-3.403692921576052</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-1.021730968590326</v>
+        <v>-1.143697472638273</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-8.794742914692762</v>
+        <v>-8.575705002021245</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-1.549886262354384</v>
+        <v>-1.646693501441618</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-7.272490932993087</v>
+        <v>-7.116607075895786</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-7.47888481963782</v>
+        <v>-4.998556969505636</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-9.884171071535654</v>
+        <v>-9.590474391240747</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.5530191019764175</v>
+        <v>-0.6879076289043269</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-2.766445467756895</v>
+        <v>-2.764611200533899</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.01774</t>
+          <t>X ≈ -0.0177</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2.228392565997858</v>
+        <v>3.478174112591418</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>10.02867245569173</v>
+        <v>9.877057950080911</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>7.755467566640803</v>
+        <v>7.491933171971326</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>2.241731823674996</v>
+        <v>3.633991599562499</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.1771658422255982</v>
+        <v>1.1513988277786</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>3.885522981272729</v>
+        <v>3.419857318960162</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.03488282694308253</v>
+        <v>-0.6329235343294073</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-2.315578267573002</v>
+        <v>-3.095361064667259</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>3.276059643476145</v>
+        <v>2.859274926257172</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-1.341849687326594</v>
+        <v>-1.958875262257735</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.338577088861058</v>
+        <v>-2.163415124301061</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-1.512788259713538</v>
+        <v>-2.10578162141335</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-1.933245081451545</v>
+        <v>-2.501397838457486</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-3.594793373878325</v>
+        <v>-4.252983293555182</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.01609</t>
+          <t>X ≈ -0.01605</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-4.466307618938174</v>
+        <v>-3.813515157416354</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-3.414832536082386</v>
+        <v>-4.080649644056599</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-2.480252187181087</v>
+        <v>-3.162693196566991</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1.639339277276797</v>
+        <v>0.9039118236652044</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>3.763362903671208</v>
+        <v>3.04167007144963</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>4.061012204889622</v>
+        <v>3.31459894040642</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>6.639270193673077</v>
+        <v>5.881658433999668</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>3.511964573252413</v>
+        <v>2.790409324689712</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>7.446622202718054</v>
+        <v>6.696306337102648</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>6.599657400555493</v>
+        <v>5.875202719494865</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>6.396755844508391</v>
+        <v>5.672671567582356</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>6.432808947649271</v>
+        <v>5.732310465192171</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>4.681410655529447</v>
+        <v>4.02325337682705</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>3.575017946877246</v>
+        <v>2.957543022233374</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.01443</t>
+          <t>X ≈ -0.01441</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-3.008319748200712</v>
+        <v>-4.075211552741649</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-4.614840328196841</v>
+        <v>-3.55543031142944</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-3.938067936392919</v>
+        <v>-2.899913779610301</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-1.663903285841926</v>
+        <v>-0.6709611259278958</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-1.128554387620063</v>
+        <v>-0.1090192595481483</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-1.905179336787967</v>
+        <v>-0.8873230590589998</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.9171136159316546</v>
+        <v>-0.9482594009689009</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.3101467481870017</v>
+        <v>-0.3626681601872477</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>3.923980425766601</v>
+        <v>3.805001722722103</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>5.224471222155444</v>
+        <v>5.086292606956576</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.3507828559560906</v>
+        <v>0.6764409218969973</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>6.131746748189684</v>
+        <v>5.995196749163057</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>5.713341215065704</v>
+        <v>6.65408895815326</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>8.091146979135793</v>
+        <v>9.010174601180758</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.01279</t>
+          <t>X ≈ -0.01275</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.881454052213968</v>
+        <v>2.481289738204829</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>4.147336250425454</v>
+        <v>3.894552797784492</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>3.754240974222988</v>
+        <v>3.502418879724431</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.955704385200427</v>
+        <v>-1.353211660320746</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>5.286587715773109</v>
+        <v>5.141315806224135</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>7.522223549469786</v>
+        <v>7.4105228321353</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>5.501456365509142</v>
+        <v>6.35372416574522</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>5.036593537773662</v>
+        <v>5.890317358768471</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>7.885295863947405</v>
+        <v>8.850491417868291</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>6.068849862120743</v>
+        <v>7.031256585724911</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>6.836163286745418</v>
+        <v>6.829282391805037</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>6.872372170726138</v>
+        <v>7.888734154265897</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>5.483652868092548</v>
+        <v>5.49641479179148</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>8.623561636197188</v>
+        <v>8.747016706443908</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.01113</t>
+          <t>X ≈ -0.01111</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.3346732716899439</v>
+        <v>-0.06239198452318817</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>4.34404044542724</v>
+        <v>3.935535667293856</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.845015021630026</v>
+        <v>1.452130877007534</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>1.2739138514589</v>
+        <v>0.8854791737066563</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>4.951544152760327</v>
+        <v>4.582453277120656</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>6.654754385715066</v>
+        <v>6.251216741866081</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>9.383351623761698</v>
+        <v>8.984051719354746</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>3.295514629859611</v>
+        <v>2.936630919045783</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>6.047935369130848</v>
+        <v>5.693263762902482</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>6.607897263228523</v>
+        <v>6.269341648658568</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>5.701768436191372</v>
+        <v>5.368593299626035</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>8.553086423343096</v>
+        <v>8.223906560197896</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>7.431576937530963</v>
+        <v>7.13220849111822</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>6.251074284905577</v>
+        <v>5.984778944206148</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.009476</t>
+          <t>X ≈ -0.009453</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>148</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>8.29780624057792</v>
+        <v>8.268894137659764</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.03828359785476465</v>
+        <v>-0.03940981276699063</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2.261858014514594</v>
+        <v>2.261780445661273</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>3.066953960093819</v>
+        <v>3.740217698461066</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>2.530188087927755</v>
+        <v>3.252530144927697</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.479181033366771</v>
+        <v>2.177205996473269</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>1.394867560945478</v>
+        <v>1.442808249680972</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>4.301978889506479</v>
+        <v>4.351176127653467</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>2.217632251497243</v>
+        <v>2.290800871599863</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>6.093932128726244</v>
+        <v>6.19318490516882</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>5.216415633943377</v>
+        <v>5.316249414623243</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>3.226532730823294</v>
+        <v>3.350160401151335</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>3.483184531599555</v>
+        <v>3.631830971438646</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>7.764207136066126</v>
+        <v>7.936205895633101</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.007826</t>
+          <t>X ≈ -0.007801</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.3656949720400178</v>
+        <v>0.3113566761988054</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.3104673921849681</v>
+        <v>0.5435012505667132</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.599858446680372</v>
+        <v>0.1506225174549556</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.596743711753859</v>
+        <v>1.82253286175564</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>2.609701448212846</v>
+        <v>1.848427689604023</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.8396572686443236</v>
+        <v>0.06428315616349067</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>2.306178971280126</v>
+        <v>2.575308789121181</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>3.392584646143547</v>
+        <v>3.655034516966985</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>2.297548222989406</v>
+        <v>3.104028307492563</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>4.037126075030159</v>
+        <v>4.856574168471994</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>7.457837399068168</v>
+        <v>8.259429318172479</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>6.976899188936123</v>
+        <v>7.290033973187484</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>3.451554194126558</v>
+        <v>3.805782975420783</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>2.642375459830738</v>
+        <v>3.025367221907828</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.006174</t>
+          <t>X ≈ -0.00615</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.421762858573125</v>
+        <v>-0.8154078944828669</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.764779406272893</v>
+        <v>-1.551674142357875</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.477739322041387</v>
+        <v>-0.8679637050528228</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.9140208092780284</v>
+        <v>0.5340854463242408</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-2.567972589613397</v>
+        <v>-2.075603633866606</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-3.534492813981132</v>
+        <v>-3.077217759818623</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-2.778752285703263</v>
+        <v>-2.714773872295417</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.561116078755553</v>
+        <v>-1.481533624057271</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.62299473827732</v>
+        <v>-1.944286636463438</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.05613459657750752</v>
+        <v>-0.2176781510607526</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.412515603166369</v>
+        <v>-1.696611018698668</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-2.221577809333994</v>
+        <v>-2.063896325333268</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.1109768666387794</v>
+        <v>0.09329193472657238</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.1151023350629004</v>
+        <v>0.3427613872949777</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.004521</t>
+          <t>X ≈ -0.0045</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.003773236471147</v>
+        <v>0.9034766045225169</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-1.490925789718261</v>
+        <v>-1.523100067494177</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-2.324044068404518</v>
+        <v>-1.916295817409335</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.756777469953676</v>
+        <v>-0.9357417575494225</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.860780783768945</v>
+        <v>-0.9981363953280535</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.562532655007175</v>
+        <v>-0.726122674021461</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.9807743759412517</v>
+        <v>1.769851760714126</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>3.576854112464204</v>
+        <v>4.290700976721773</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.2520933387809663</v>
+        <v>0.8422358632912008</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.5159598314735092</v>
+        <v>0.8733931935284147</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.312226002547753</v>
+        <v>0.6703616624046944</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.7854087182247156</v>
+        <v>1.156215089737501</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.5106221164785225</v>
+        <v>-0.5193948888687032</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.039017140842148</v>
+        <v>-1.979479020051819</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.002868</t>
+          <t>X ≈ -0.002849</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.2933947299647457</v>
+        <v>0.2863973333600569</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-3.2846310887182</v>
+        <v>-2.879976026534905</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.703261813850268</v>
+        <v>-2.078380132575056</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-2.365177186087344</v>
+        <v>-3.145102843815508</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-2.111778882851155</v>
+        <v>-2.837186037285278</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.419884514863746</v>
+        <v>-2.167353936147222</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.07798330047592827</v>
+        <v>-0.6348002029098723</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.196304191442891</v>
+        <v>0.8950941639174346</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.7389012933583032</v>
+        <v>0.06020602002339359</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.474605969036055</v>
+        <v>1.234552984396721</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.3139244374792796</v>
+        <v>-0.9656926520038454</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.6756998465083157</v>
+        <v>-1.307116360042784</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.681421741441298</v>
+        <v>1.496830458597323</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.07577570391631383</v>
+        <v>-0.2529832935560847</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.001216</t>
+          <t>X ≈ -0.001199</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>275</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-4.099525777069864</v>
+        <v>-3.95631296674037</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-4.976327501066876</v>
+        <v>-5.175158328868839</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-5.3736503678575</v>
+        <v>-5.206870259505337</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-5.246109434159884</v>
+        <v>-5.241778935837736</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-2.52331114664689</v>
+        <v>-2.4728426495655</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-3.678471777946001</v>
+        <v>-3.65136825920969</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-3.040836684863265</v>
+        <v>-2.628579004753185</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-4.96069954804922</v>
+        <v>-5.271040990308904</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-7.199745242760315</v>
+        <v>-7.124102274132923</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-5.145062873561045</v>
+        <v>-5.408989213556737</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-5.713784365360709</v>
+        <v>-5.614050282193283</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-4.954787687181252</v>
+        <v>-4.831241211560375</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-6.103191216362127</v>
+        <v>-5.954597525328055</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-6.243163871304574</v>
+        <v>-6.071165111737912</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.000436</t>
+          <t>X ≈ 0.0004519</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>243</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.615685099293827</v>
+        <v>1.800871171975807</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.222054158357388</v>
+        <v>-0.9960706145632869</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-3.667238469790718</v>
+        <v>-3.436950457766542</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.791405322744936</v>
+        <v>2.015271923435364</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.253594792768034</v>
+        <v>1.52633782106539</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.1412347387881</v>
+        <v>1.389475062183415</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.058710108651667</v>
+        <v>0.9157916359870413</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.238880144611066</v>
+        <v>-1.189403751020322</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.299582230929481</v>
+        <v>-1.226285779683543</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-4.20261770535182</v>
+        <v>-4.103553142297812</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-5.229660568728917</v>
+        <v>-5.129975264867703</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-3.142144697014224</v>
+        <v>-3.018634209584384</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-3.56297906131806</v>
+        <v>-3.414408060685545</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.692471765056816</v>
+        <v>-1.520473005490253</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.002089</t>
+          <t>X ≈ 0.002103</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-4.854244762675144</v>
+        <v>-5.038387819001684</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.805398328028105</v>
+        <v>-2.998829064752471</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-3.934819276776729</v>
+        <v>-3.753830220995809</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-3.441293937217814</v>
+        <v>-3.263466955310079</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-3.982055668896031</v>
+        <v>-3.755120502821356</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-4.420536087858018</v>
+        <v>-4.208909759711126</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-5.240187785909086</v>
+        <v>-5.161592281943939</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-5.708221144710272</v>
+        <v>-5.628092668135622</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-4.668522250124091</v>
+        <v>-4.579909115496037</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-4.051252197647628</v>
+        <v>-3.954067691777134</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-6.095642045954399</v>
+        <v>-5.973528660942407</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-7.325897785197093</v>
+        <v>-7.3720385956752</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-7.749436837186231</v>
+        <v>-7.770592014472051</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-8.998511464887542</v>
+        <v>-8.980256020828818</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.003741</t>
+          <t>X ≈ 0.003753</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>232</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.7375515865778652</v>
+        <v>0.7083527356030359</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>2.131080247034994</v>
+        <v>2.129843472978067</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>3.453243899904344</v>
+        <v>3.022533043140228</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.00786899718716</v>
+        <v>1.008013591724662</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.03944790152847588</v>
+        <v>-0.3394003676092368</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2.056886801327529</v>
+        <v>2.316715524029306</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.114984856145895</v>
+        <v>0.5350830747997222</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.6451385903139411</v>
+        <v>-0.7862437714999686</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.01563248443145</v>
+        <v>0.4647632796211099</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.025894352046862</v>
+        <v>0.501532295024596</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.2295768635831621</v>
+        <v>-0.9898654370883619</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.2347450343015112</v>
+        <v>-0.5027044165512251</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.107465061895404</v>
+        <v>0.3945058725336921</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2.626742084808285</v>
+        <v>1.936671878857702</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.005393</t>
+          <t>X ≈ 0.005404</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.7141621031353722</v>
+        <v>-0.1858862669515915</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.02787517609840506</v>
+        <v>-0.2236942674149986</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>2.767806765254882</v>
+        <v>3.657352785502027</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.6323269265745353</v>
+        <v>-0.09755026119538002</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-2.743319985628702</v>
+        <v>-1.924940366222572</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-4.413575242719517</v>
+        <v>-4.373220598455063</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-6.46634860067757</v>
+        <v>-5.212293177936267</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-3.789237119828421</v>
+        <v>-3.130229372786339</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-5.02947405080193</v>
+        <v>-3.948958081480555</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-3.912969675248512</v>
+        <v>-2.829072808949519</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.155527152191667</v>
+        <v>-1.082791350162104</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-4.086502299077999</v>
+        <v>-2.97670792322581</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-3.497858158835186</v>
+        <v>-2.983594119785259</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-6.031281265721226</v>
+        <v>-5.081108293556092</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.007046</t>
+          <t>X ≈ 0.007055</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>3.683085612549597</v>
+        <v>3.266019764335049</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>3.353985188083435</v>
+        <v>3.412261843878426</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.8321939498355917</v>
+        <v>0.4552755915306079</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>3.517587598822928</v>
+        <v>3.144255899062088</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.4212836895481828</v>
+        <v>0.09798649065152176</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>2.424711752425566</v>
+        <v>2.077874186444134</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>3.19877091315054</v>
+        <v>2.437506145030163</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>5.294010751067681</v>
+        <v>4.533883649250917</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>3.096635274272558</v>
+        <v>2.365253971858884</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.1110407906296587</v>
+        <v>-0.5951043982095996</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>1.182291034265475</v>
+        <v>0.4886294816804266</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>2.499438101631533</v>
+        <v>1.83081242009434</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>1.221715861779437</v>
+        <v>1.008779779246183</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>2.976727348586749</v>
+        <v>2.11611541889031</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.008699</t>
+          <t>X ≈ 0.008705</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-2.976161598263928</v>
+        <v>-2.492311724157702</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>5.759049065564831</v>
+        <v>6.156695921248613</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>3.949452510561777</v>
+        <v>4.370632970642838</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.722205496633066</v>
+        <v>2.177767643607652</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3.806543248471364</v>
+        <v>4.014579517552924</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.95392749232294</v>
+        <v>2.431483694425012</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.601705527112486</v>
+        <v>-2.275499042961982</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.1730395737428267</v>
+        <v>-0.887106284722158</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1.187779217601701</v>
+        <v>0.4696783553305508</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>1.759661369139131</v>
+        <v>1.041239940021121</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.1331592630116489</v>
+        <v>-0.5512832698810755</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.3063962339221362</v>
+        <v>-0.9627542277214047</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.252613437946394</v>
+        <v>-0.8918749918655919</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1.394923160147329</v>
+        <v>0.7563625008363815</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>160</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.559066512351173</v>
+        <v>1.230881571396814</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>2.434016571889131</v>
+        <v>2.148008649218177</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.7887632208692992</v>
+        <v>0.5183128516880728</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>3.768351635235099</v>
+        <v>3.121464346788237</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>7.605062082139412</v>
+        <v>6.969558139454442</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>8.527436111774534</v>
+        <v>8.482356973852688</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>4.692725752508331</v>
+        <v>4.705716444253262</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>3.600657108721627</v>
+        <v>3.615821519716476</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>5.414674952198844</v>
+        <v>5.444217372712984</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>5.189756155868999</v>
+        <v>5.248517391278014</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>8.735054997608799</v>
+        <v>8.797311609421385</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>9.394433149964094</v>
+        <v>9.488838842371585</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>8.349282296650713</v>
+        <v>8.486328403643121</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>4.200017946877239</v>
+        <v>3.747016706443908</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>128</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-6.004639881735407</v>
+        <v>-6.400335433902946</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>2.50719395148711</v>
+        <v>2.841794141588515</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-2.14312350835322</v>
+        <v>-2.976700844314763</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2.674601635235184</v>
+        <v>2.58024565491985</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.2074379178605312</v>
+        <v>-0.2301118000040958</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>2.433686111774534</v>
+        <v>2.366087493218316</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>5.473975752508387</v>
+        <v>5.399858245883635</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.100657108721627</v>
+        <v>1.06512738547503</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.2584249521988298</v>
+        <v>-0.09921326045974865</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-2.935243844131008</v>
+        <v>-3.248880020718758</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.577445002391201</v>
+        <v>-1.906085121745761</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-3.105566850035835</v>
+        <v>-3.404756960630927</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.4007177033492866</v>
+        <v>-0.6919812272437866</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>4.512517946877225</v>
+        <v>4.684516706443887</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>125</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>4.312432776788256</v>
+        <v>4.26187454015794</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-2.09210212359816</v>
+        <v>-2.061577310001553</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1.513126491646752</v>
+        <v>1.522889432599982</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-3.95664836476486</v>
+        <v>-3.911548393760988</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.4949379178605255</v>
+        <v>-0.445834204478416</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-3.397563888225463</v>
+        <v>-3.342700581124859</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-3.48227424749161</v>
+        <v>-3.405939048203813</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-5.549342891278371</v>
+        <v>-5.447559433832538</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-8.810325047801122</v>
+        <v>-8.649019182727592</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-4.060243844131008</v>
+        <v>-3.943764786195302</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-7.464945002391204</v>
+        <v>-7.321975377132702</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-4.230566850035878</v>
+        <v>-4.09713997473591</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-3.850717703349261</v>
+        <v>-3.702028155571433</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-2.024982053122727</v>
+        <v>-1.852983293556065</v>
       </c>
     </row>
     <row r="29">
@@ -1771,98 +1771,98 @@
         <v>83</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>4.134098984480659</v>
+        <v>4.068092579404379</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>7.353681008931936</v>
+        <v>7.26093657461746</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>11.77818673261064</v>
+        <v>11.63380878769551</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>8.293954044873701</v>
+        <v>8.182853378505534</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>6.550845214669529</v>
+        <v>6.489011728613271</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>9.257857798521513</v>
+        <v>9.138044188896593</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>6.763508885038483</v>
+        <v>6.701141158206738</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>7.50125951836015</v>
+        <v>7.439900906763739</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>9.8499159160543</v>
+        <v>9.788586118067393</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>7.795177842615999</v>
+        <v>7.784661405825943</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>12.40975379278956</v>
+        <v>12.43004378845248</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>10.03449339092794</v>
+        <v>10.11895559681818</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>8.409523260506106</v>
+        <v>8.558212808283933</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>6.225620356515805</v>
+        <v>6.397619116082467</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.01696</t>
+          <t>X ≈ 0.01695</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>53</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-6.307331124873961</v>
+        <v>-6.235821437908463</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-6.922290802843435</v>
+        <v>-7.823158333227056</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>2.116900076552497</v>
+        <v>1.07345880257607</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-5.300044591179926</v>
+        <v>-6.227277331438387</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-5.838334144275592</v>
+        <v>-6.712366662227559</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-3.654167661810391</v>
+        <v>-4.579846194520051</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-7.512462926736916</v>
+        <v>-8.358585578135205</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-9.866324023353762</v>
+        <v>-10.68692649418232</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-6.153721274216295</v>
+        <v>-7.008589015704587</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-10.7772249762065</v>
+        <v>-11.57771156961373</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-7.208341228806347</v>
+        <v>-6.238700744360877</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-3.400378170790539</v>
+        <v>-2.393662681837782</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.04694411844359081</v>
+        <v>0.1017454293342368</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-7.368378279537822</v>
+        <v>-7.19637951997116</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>36</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>3.07463952502124</v>
+        <v>1.300608443119756</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>1.463453431957333</v>
+        <v>-0.4081967827396795</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>3.846459824980116</v>
+        <v>2.143347194328122</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>12.31001830190177</v>
+        <v>10.52281247507381</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>14.54950652658389</v>
+        <v>10.15919147482536</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>9.291325000663463</v>
+        <v>10.51572908744669</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>3.651059085841702</v>
+        <v>4.773889301962129</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>8.739545997610477</v>
+        <v>12.47388568730738</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>3.123008285532187</v>
+        <v>6.923233569516221</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-3.28246606635323</v>
+        <v>-0.6017494930227514</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.7093894468356439</v>
+        <v>0.5890521481227182</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-6.230566850035878</v>
+        <v>-6.106870229007633</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-3.872939925571551</v>
+        <v>-3.724250377793723</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>1.908351280210582</v>
+        <v>2.080350039777244</v>
       </c>
     </row>
     <row r="32">
@@ -1927,150 +1927,150 @@
         <v>31</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-10.54543215956666</v>
+        <v>-10.57462795391929</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-8.930811801017583</v>
+        <v>-8.931998587462239</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-15.77719608899838</v>
+        <v>-15.7773494790027</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-9.195358042184218</v>
+        <v>-9.195852534562221</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-3.282034692054104</v>
+        <v>-3.233488772288332</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-2.984660662418996</v>
+        <v>-2.960703253469383</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.1564354299277184</v>
+        <v>0.2044471089180391</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>6.140979689366745</v>
+        <v>6.190227251760462</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>2.854191081231072</v>
+        <v>2.927448191010768</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>2.004272284901255</v>
+        <v>2.103619610195828</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>1.799571126641062</v>
+        <v>1.899479162659738</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>1.833949278996343</v>
+        <v>1.957645900024588</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>1.413798425682977</v>
+        <v>1.562487973460804</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>1.639534075909509</v>
+        <v>1.811532835476171</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.02192</t>
+          <t>X ≈ 0.02191</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>23</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>8.388649186856959</v>
+        <v>8.359453392504328</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>2.429637006836664</v>
+        <v>2.428450220392008</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>2.034865622081561</v>
+        <v>2.03471223207724</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>2.165090765669923</v>
+        <v>2.16459627329192</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>10.32245338648728</v>
+        <v>10.37099930625305</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1.924175242209287</v>
+        <v>1.9481326511589</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>6.187290969899678</v>
+        <v>6.235302648889999</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>14.41587450002604</v>
+        <v>14.46512206241976</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>18.70271843045978</v>
+        <v>18.77597554023948</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>13.50497354717334</v>
+        <v>13.60432087246791</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>13.30027238891314</v>
+        <v>13.40018042493182</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>13.33465054126854</v>
+        <v>13.45834716229678</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>17.26232577491157</v>
+        <v>17.4110153226894</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>13.14023533818153</v>
+        <v>13.3122340977482</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.02357</t>
+          <t>X ≈ 0.02356</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>22</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-16.11727966689799</v>
+        <v>-16.14647546125062</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-17.72846575996181</v>
+        <v>-17.72965254640647</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-4.48687350835322</v>
+        <v>-4.487026898357541</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-17.99301200112849</v>
+        <v>-17.99350649350649</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-23.07675609967874</v>
+        <v>-23.02821017991296</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-27.32483661549822</v>
+        <v>-27.30087920654861</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-18.31863788385527</v>
+        <v>-18.27062620486495</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-23.33116107309656</v>
+        <v>-23.28191351070284</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-14.30123413871024</v>
+        <v>-14.22797702893054</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-10.60569838958556</v>
+        <v>-10.50635106429098</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-10.81039954784575</v>
+        <v>-10.71049151182707</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-19.86693048639955</v>
+        <v>-19.7432338653713</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-15.74162679425837</v>
+        <v>-15.59293724648055</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-20.06134568948639</v>
+        <v>-19.88934692991972</v>
       </c>
     </row>
   </sheetData>
@@ -2210,1093 +2210,1093 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.02352</t>
+          <t>X &gt; -0.02348</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4084</v>
+        <v>4095</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.02091457722742973</v>
+        <v>0.02153374473326863</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.03387443890181885</v>
+        <v>0.0338111630031861</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.005799027278740709</v>
+        <v>-0.005779942682920591</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.1377336577070523</v>
+        <v>0.137376022272484</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.1258292455892374</v>
+        <v>0.1243682358233471</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.09451822321148029</v>
+        <v>0.09371011833565035</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.1209523474729295</v>
+        <v>0.1195160760623111</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.08293094735243756</v>
+        <v>0.0815676801375318</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.03545631683567763</v>
+        <v>0.03366376929562165</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.006292359391501634</v>
+        <v>0.003972961524631557</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.03788358815092607</v>
+        <v>-0.04009797174100527</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.01025547008160288</v>
+        <v>0.007359695327245674</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.004450873483918372</v>
+        <v>-0.007887530571458967</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.03926868145119755</v>
+        <v>0.0351729946001953</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.02187</t>
+          <t>X &gt; -0.02183</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4058</v>
+        <v>4068</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.03679910594579638</v>
+        <v>-0.04748011697225252</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.08480205330599233</v>
+        <v>0.07337775662382739</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.05089415224606597</v>
+        <v>-0.06192270615356676</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.06813039629708584</v>
+        <v>0.05678553912981954</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.03498585887905392</v>
+        <v>0.02238406273426108</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.05073911226641314</v>
+        <v>0.0387585845121734</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.07787335398437989</v>
+        <v>0.0651239345661665</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.05583895427050578</v>
+        <v>-0.06818565779972374</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.004811880191006424</v>
+        <v>-0.01799109048891978</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.05335068805025855</v>
+        <v>-0.0669868921173844</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.09651358155888801</v>
+        <v>-0.1100136305827917</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.0483008401836571</v>
+        <v>-0.06264418478158973</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.03578791768779155</v>
+        <v>-0.05081164045718367</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.04252764208283821</v>
+        <v>-0.05829302806936454</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.02022</t>
+          <t>X &gt; -0.02018</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4031</v>
+        <v>4041</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.05757280600418113</v>
+        <v>-0.04341226889290795</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.07559513091580072</v>
+        <v>0.08879843266627319</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.008892310926206903</v>
+        <v>-0.0200969872025567</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.1100677946016333</v>
+        <v>0.09854709595513356</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.1298145573869789</v>
+        <v>0.1165709648681741</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.1684673076150958</v>
+        <v>0.1559563757500868</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.1220843458714214</v>
+        <v>0.1088204354512499</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.05892921775842552</v>
+        <v>-0.07167921818537337</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.03193059785071029</v>
+        <v>-0.04561959397794624</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.02554743768739343</v>
+        <v>-0.04000653119737763</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.06762224582204368</v>
+        <v>-0.08195091296006041</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.04410515898702982</v>
+        <v>-0.05938074100367885</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.003892306523894717</v>
+        <v>-0.02008852172682651</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.01262648073980444</v>
+        <v>-0.004529940425676671</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.01857</t>
+          <t>X &gt; -0.01853</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3990</v>
+        <v>3998</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.09520531357208029</v>
+        <v>-0.07929656684660102</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.1307864321239549</v>
+        <v>0.1211749303561689</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.05048260607878774</v>
+        <v>-0.05948885894621725</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.1183516352351361</v>
+        <v>0.1338751069289899</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.1688280236248261</v>
+        <v>0.1823077772982842</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.2048373123748348</v>
+        <v>0.1942417483826588</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.1338378365714163</v>
+        <v>0.1222917386147913</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.03083728890180737</v>
+        <v>0.01978479099545893</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.01633255718788718</v>
+        <v>-0.02839943939542167</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.04891990148742309</v>
+        <v>0.03610498041393839</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.008533585136966337</v>
+        <v>-0.02907095787465153</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.05700830026472659</v>
+        <v>0.04312977099236548</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.001750349770233584</v>
+        <v>-0.01290587500130869</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.0411833604110754</v>
+        <v>0.02515577597868202</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.01691</t>
+          <t>X &gt; -0.01688</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3937</v>
+        <v>3948</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.1264856507875223</v>
+        <v>-0.1243506534656191</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.002459176016522235</v>
+        <v>-0.002379819133750516</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.1555665174717618</v>
+        <v>-0.1551249029041415</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.0897666339683596</v>
+        <v>0.08954739045693572</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.1734858023624639</v>
+        <v>0.1700345877025384</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.1552878228011494</v>
+        <v>0.1533904873571146</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.1351699715753014</v>
+        <v>0.1318562684139906</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.062424798298089</v>
+        <v>0.05923699281489547</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.06065482963777669</v>
+        <v>-0.06497079660986316</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.06764247913719856</v>
+        <v>0.06137068764130049</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.004090530603725995</v>
+        <v>-0.002040256678782271</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.07814094382042924</v>
+        <v>0.07034496086578912</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.02779931036326388</v>
+        <v>0.01860998066556618</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.09013097710330698</v>
+        <v>0.07933686855130162</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.01526</t>
+          <t>X &gt; -0.01523</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3862</v>
+        <v>3872</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.04220635311499166</v>
+        <v>-0.05193936671452803</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.06380907929288782</v>
+        <v>0.07766886544634133</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.1104211458435316</v>
+        <v>-0.09609205416489885</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.05967394928473624</v>
+        <v>0.07356296459850142</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.1037704262365864</v>
+        <v>0.1136698416372539</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.07943869575386486</v>
+        <v>0.09134197433238711</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.008860412627257119</v>
+        <v>0.01899858127956122</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.004565228403507149</v>
+        <v>0.005629271424780313</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.2064460718507988</v>
+        <v>-0.1976818147302524</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.05920918298253497</v>
+        <v>-0.0527437840583076</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.1200549635813672</v>
+        <v>-0.1134240631467165</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.0452666429965447</v>
+        <v>-0.04078865957036015</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.06257377376088158</v>
+        <v>-0.05999355706900644</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.02245450824441519</v>
+        <v>0.02284315272490289</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.01361</t>
+          <t>X &gt; -0.01358</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3769</v>
+        <v>3777</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.03098243588552663</v>
+        <v>0.04925492973042367</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.1792546603214191</v>
+        <v>0.1690494378062013</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.01597403745375203</v>
+        <v>-0.02556966498900692</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.1022031832637182</v>
+        <v>0.0922894111433834</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.1341780164962429</v>
+        <v>0.1192709707377588</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.128409106214562</v>
+        <v>0.1159575894163538</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.03170880335582638</v>
+        <v>0.04332728350714632</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.002974989516324911</v>
+        <v>0.01489277579417347</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.3083642634874195</v>
+        <v>-0.2983582606021002</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.1895838918384101</v>
+        <v>-0.1820020464746293</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.1143617574283198</v>
+        <v>-0.1332909346264941</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.1976843255065717</v>
+        <v>-0.1926071964593419</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.2050943611742184</v>
+        <v>-0.2288677532421914</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.1766403179144831</v>
+        <v>-0.2032083398891587</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.01196</t>
+          <t>X &gt; -0.01193</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3666</v>
+        <v>3677</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.02100844695185344</v>
+        <v>-0.01688689263765752</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.06776737069220218</v>
+        <v>0.06773033636540049</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.1219020642411763</v>
+        <v>-0.1215171369692527</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.1319261727759411</v>
+        <v>0.1316013793637865</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.01058417636395603</v>
+        <v>-0.01730898127438252</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.07932763346227034</v>
+        <v>-0.08242601794614046</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.1219693196397458</v>
+        <v>-0.1282907986858959</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.1384496450910078</v>
+        <v>-0.1448957633131087</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.5385734814704506</v>
+        <v>-0.5471711428014601</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.3654209558476254</v>
+        <v>-0.378174432446869</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.3096438304097404</v>
+        <v>-0.3226456620246978</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.3963247562517935</v>
+        <v>-0.4123880327586491</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.3649255026402614</v>
+        <v>-0.3845730169091368</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.4238909456486653</v>
+        <v>-0.446619409955332</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.0103</t>
+          <t>X &gt; -0.01028</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3524</v>
+        <v>3534</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.03534068419565273</v>
+        <v>-0.01504557171529086</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.1045455625122145</v>
+        <v>-0.08877678370330244</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.2011592226389354</v>
+        <v>-0.185193329951332</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.08590964315818184</v>
+        <v>0.1010964205095064</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.2105337287861104</v>
+        <v>-0.2034340528506391</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.350678271011418</v>
+        <v>-0.3387109400324846</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.504987359924371</v>
+        <v>-0.4970132039150457</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.2768216448194423</v>
+        <v>-0.2695868543083861</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.803977640603641</v>
+        <v>-0.7996844963712633</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.6464116445845249</v>
+        <v>-0.6471599445006575</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.5518744041490677</v>
+        <v>-0.5529363161039313</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.7569423463489784</v>
+        <v>-0.7618476045732407</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.6790864976755344</v>
+        <v>-0.6887325402956463</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.692859465154541</v>
+        <v>-0.7068599206075916</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.008652</t>
+          <t>X &gt; -0.008626</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3376</v>
+        <v>3386</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.4006563669167633</v>
+        <v>-0.3771315365668855</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.1074504116737458</v>
+        <v>-0.09093458396867504</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.3091350967795563</v>
+        <v>-0.292149064975149</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.04477594893496928</v>
+        <v>-0.05796735655393803</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.3306838558221443</v>
+        <v>-0.3544921453701875</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.4308972215588014</v>
+        <v>-0.4486801386747885</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.5882748386828851</v>
+        <v>-0.581801619488644</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.4775510521299395</v>
+        <v>-0.4715575930355982</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.9364415813710991</v>
+        <v>-0.9347677315926788</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.9419006488647383</v>
+        <v>-0.946147256299561</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.8047496783308361</v>
+        <v>-0.8094748536549119</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.9315733627652989</v>
+        <v>-0.9415809728092839</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.8615557252622352</v>
+        <v>-0.8775817428168153</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.063607645539811</v>
+        <v>-1.084643069102455</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.007</t>
+          <t>X &gt; -0.006975</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3183</v>
+        <v>3192</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.4471237902339738</v>
+        <v>-0.4189757449868594</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.132790699498031</v>
+        <v>-0.1294936541127427</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.2915071965185305</v>
+        <v>-0.3190593679173332</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.1443088721247108</v>
+        <v>-0.1722584099223781</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.5089730055798469</v>
+        <v>-0.4883788771950606</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.5079368120737868</v>
+        <v>-0.4798564792758597</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.7637789496859853</v>
+        <v>-0.7736811368039085</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.7122152650632643</v>
+        <v>-0.722359243831491</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.132533328855104</v>
+        <v>-1.180233405647357</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.243802049339671</v>
+        <v>-1.298818921840187</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.305748517770994</v>
+        <v>-1.36065511973716</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.411100601998207</v>
+        <v>-1.441873359878009</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.123079512394511</v>
+        <v>-1.162222330328746</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.28831852814632</v>
+        <v>-1.334436927641306</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.005347</t>
+          <t>X &gt; -0.005325</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2946</v>
+        <v>2957</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.368715962943952</v>
+        <v>-0.3874703154530224</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.001500365653626545</v>
+        <v>-0.01646950303475592</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.276525182347136</v>
+        <v>-0.2754366018615855</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.2294494473088378</v>
+        <v>-0.2283932784438392</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.3433304728520881</v>
+        <v>-0.362238255680758</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.2644562375822659</v>
+        <v>-0.2734378452117667</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.6016782434279691</v>
+        <v>-0.6194177641828276</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.643922837077838</v>
+        <v>-0.6620258047537035</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.093076657425001</v>
+        <v>-1.119512232417129</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.34837943735134</v>
+        <v>-1.384739815020154</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.29715931232677</v>
+        <v>-1.333955885291445</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.345899278801141</v>
+        <v>-1.392439678145855</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.204501212002157</v>
+        <v>-1.262001110270582</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.401221021215086</v>
+        <v>-1.467727967211822</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.003695</t>
+          <t>X &gt; -0.003674</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2718</v>
+        <v>2723</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.4838475072657573</v>
+        <v>-0.4984073625607266</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.1234403983959496</v>
+        <v>0.1130022384575256</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.1047686311988372</v>
+        <v>-0.1344299707788963</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.1013292158286916</v>
+        <v>-0.1676075479588164</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.2160388352917408</v>
+        <v>-0.3075925837463203</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.1555668250830351</v>
+        <v>-0.2345365415241147</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.7344226132646838</v>
+        <v>-0.824738758977503</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.9979835966420794</v>
+        <v>-1.087636552776196</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.205916524656409</v>
+        <v>-1.288094330983334</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.504769927892944</v>
+        <v>-1.578791641682052</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.432162936974073</v>
+        <v>-1.50619617400276</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.524684497094697</v>
+        <v>-1.61145738497094</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.262707405445639</v>
+        <v>-1.325816701826966</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.347719359966014</v>
+        <v>-1.423750829362191</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.002042</t>
+          <t>X &gt; -0.002024</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2466</v>
+        <v>2473</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.5632737212893062</v>
+        <v>-0.5777446751285353</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.4717104773711256</v>
+        <v>0.4155677727268881</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.05858103710131957</v>
+        <v>0.06208743336548395</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.1300129125188931</v>
+        <v>0.1333927852252401</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.02231357495720232</v>
+        <v>-0.0518714501495765</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.02636647722223273</v>
+        <v>-0.03914456875590133</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.8174421956907381</v>
+        <v>-0.843939987856146</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.222217385205504</v>
+        <v>-1.288074352684575</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.404657031606817</v>
+        <v>-1.424396428739769</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-1.809231698382021</v>
+        <v>-1.863197689607532</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.546435484367706</v>
+        <v>-1.560836643270747</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.611442052629073</v>
+        <v>-1.642223764361169</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.563567318266195</v>
+        <v>-1.61116315961349</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.477699003649924</v>
+        <v>-1.542105816807208</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -0.00039</t>
+          <t>X &gt; -0.0003732</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2191</v>
+        <v>2198</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.1194264755843051</v>
+        <v>-0.1550393611188667</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.155512596983371</v>
+        <v>1.115044423290499</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.7403992189195066</v>
+        <v>0.7213064349757943</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.8047886520609708</v>
+        <v>0.8059006211180062</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.291595294150369</v>
+        <v>0.2510253104688758</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.4320219105911036</v>
+        <v>0.4127942460187981</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.538376251134622</v>
+        <v>-0.6206571263244456</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.7529875382032074</v>
+        <v>-0.7897505012984496</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.6772954350448828</v>
+        <v>-0.7112849148712002</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-1.390539971693649</v>
+        <v>-1.419570451624807</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.023377089902588</v>
+        <v>-1.053723926845038</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.191807160113399</v>
+        <v>-1.243233865371273</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.9937833967799463</v>
+        <v>-1.067739842701975</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.8795689997224798</v>
+        <v>-0.9754582708081401</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.001262</t>
+          <t>X &gt; 0.001277</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1948</v>
+        <v>1955</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.3358700652636628</v>
+        <v>-0.3981525373551804</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.452098182993538</v>
+        <v>1.377449003443168</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.290222606166211</v>
+        <v>1.23816394133712</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.6817148065906409</v>
+        <v>0.6555797891675681</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.1715922766123228</v>
+        <v>0.09250820557120676</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.3435523432133465</v>
+        <v>0.291396067845902</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.7376021163440925</v>
+        <v>-0.8116325990823583</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.6923756781636214</v>
+        <v>-0.7400749311284116</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.5996693100962318</v>
+        <v>-0.6472720196541104</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.039752040852314</v>
+        <v>-1.08596032690177</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.4986712965992979</v>
+        <v>-0.5470594382826377</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.9485155679845931</v>
+        <v>-1.022557505451175</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.6732933831851042</v>
+        <v>-0.7760567854283167</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.7781648046628007</v>
+        <v>-0.9077147513566004</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.002915</t>
+          <t>X &gt; 0.002928</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1676</v>
+        <v>1680</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.3974222483973975</v>
+        <v>0.3614097855333824</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>2.143052270701112</v>
+        <v>2.093804044368049</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2.138200763779871</v>
+        <v>2.055305842909476</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.350842717280322</v>
+        <v>1.297090416983849</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.845692659176926</v>
+        <v>0.7223283810521366</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.11672182606025</v>
+        <v>1.028053271761493</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.006872222476751233</v>
+        <v>-0.09958562718536967</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.1216517483880963</v>
+        <v>0.060047019869792</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.06066959186532017</v>
+        <v>-0.003536780751417723</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.5510121586039176</v>
+        <v>-0.6164784665799061</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.4096676316969905</v>
+        <v>0.3412018928075113</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.08647725008330553</v>
+        <v>0.01679207777001324</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.4751022131683058</v>
+        <v>0.3688820169449087</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.5559248681182964</v>
+        <v>0.4136833731105725</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.004567</t>
+          <t>X &gt; 0.004579</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1444</v>
+        <v>1448</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.3427754295207492</v>
+        <v>0.3058222410470819</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>2.144975753727799</v>
+        <v>2.088029771275842</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.92691959509505</v>
+        <v>1.900335739005094</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.405946528264813</v>
+        <v>1.343406593406591</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.9752278279957949</v>
+        <v>0.8924396170254951</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.9656703895907128</v>
+        <v>0.8215825241605756</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.1871151880172235</v>
+        <v>-0.2012728777796653</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.244847980090924</v>
+        <v>0.1956405720782044</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.09275934932258423</v>
+        <v>-0.07856828213707701</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.8043655592070778</v>
+        <v>-0.7956072626380859</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.5123717334317561</v>
+        <v>0.554466824116794</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.06265583322829826</v>
+        <v>0.1000263227165092</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.3735037499379104</v>
+        <v>0.3647765373201892</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.2232173928606258</v>
+        <v>0.1696686401455665</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.00622</t>
+          <t>X &gt; 0.006229</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.5683738608608024</v>
+        <v>0.4114240682682748</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>2.596861087104159</v>
+        <v>2.584507417169178</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.747436115077747</v>
+        <v>1.522989796133274</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.84100657660867</v>
+        <v>1.652873837347954</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.768934672248413</v>
+        <v>1.497514512756638</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>2.113845507747691</v>
+        <v>1.937244939755864</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.153158162248083</v>
+        <v>0.8749194014486008</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.10590479973758</v>
+        <v>0.9099213656061593</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.9609595869595609</v>
+        <v>0.7526563727554887</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.1408483781360488</v>
+        <v>-0.3588898298732204</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>1.081822419942974</v>
+        <v>0.9060927407404407</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.9482744597878039</v>
+        <v>0.7608014627846629</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>1.199828056516367</v>
+        <v>1.083889698577742</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>1.558211224188177</v>
+        <v>1.297352276913706</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.007872</t>
+          <t>X &gt; 0.00788</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.1940137436320697</v>
+        <v>-0.282132550275584</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>2.411539915943962</v>
+        <v>2.383395027780999</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.971459824980116</v>
+        <v>1.782403153455931</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.430630050250784</v>
+        <v>1.290525536639521</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>2.098799034122749</v>
+        <v>1.837545825739419</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.037754816058758</v>
+        <v>1.903077458547983</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.6524537859811659</v>
+        <v>0.4952711102551675</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.08078263173418065</v>
+        <v>0.0294383498718247</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.4382105170524042</v>
+        <v>0.3608573731818723</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.2025032583569484</v>
+        <v>-0.3014988033639554</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>1.057230729826372</v>
+        <v>1.007520206184644</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.5685963298804424</v>
+        <v>0.5008300831671804</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>1.194470581169547</v>
+        <v>1.102138511095205</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1.211001210475565</v>
+        <v>1.098424422815121</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.009525</t>
+          <t>X &gt; 0.00953</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>745</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.5939502796260783</v>
+        <v>0.352737709067739</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.463453431957376</v>
+        <v>1.299520677174201</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1.411249816043565</v>
+        <v>1.038938481136469</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1.348049621812322</v>
+        <v>1.035666730074176</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1.615129196233411</v>
+        <v>1.21219655050708</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.77827503794903</v>
+        <v>1.751293653879948</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>1.290880114924477</v>
+        <v>1.291170187823589</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.1526705315404229</v>
+        <v>0.2927142583323814</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.2259165629371083</v>
+        <v>0.3295987286452089</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.7582304213122129</v>
+        <v>-0.6871982544839668</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>1.318947615058462</v>
+        <v>1.455283889242445</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.8164130157359324</v>
+        <v>0.9212422207915623</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>1.604315853697692</v>
+        <v>1.674915544160449</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>1.158910564326909</v>
+        <v>1.19668113597411</v>
       </c>
     </row>
     <row r="27">
@@ -3309,46 +3309,46 @@
         <v>585</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.3299868655474185</v>
+        <v>0.112561609969184</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>1.198000265480317</v>
+        <v>1.067455590803192</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.581502560022848</v>
+        <v>1.181331815686455</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.686086677970188</v>
+        <v>0.4651921682378486</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.02314304606567674</v>
+        <v>-0.3624664481793758</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.06764935831093766</v>
+        <v>-0.08968092936044769</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.3604607952434122</v>
+        <v>0.3572771946120454</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.790368532304015</v>
+        <v>-0.6161697789692511</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.193231030707132</v>
+        <v>-1.069271327851958</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-2.385030168917332</v>
+        <v>-2.310641849906048</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.7093894468356439</v>
+        <v>-0.5527920684133392</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.529712149181172</v>
+        <v>-1.422032068871346</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.2404612930928778</v>
+        <v>-0.1880349815100217</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.3271546990139953</v>
+        <v>0.4991534585806576</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>457</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>2.104236807893599</v>
+        <v>1.936742838887419</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.8313114431414306</v>
+        <v>0.5704854934278742</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>2.624723865826212</v>
+        <v>2.345944902076297</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.129128440486781</v>
+        <v>-0.1272079330647671</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.02847564887905918</v>
+        <v>-0.3995373343203781</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.7682422252057748</v>
+        <v>-0.7775110345903897</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.071770965215919</v>
+        <v>-1.055086863512159</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.320021228258682</v>
+        <v>-1.087080144502885</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-1.599821765525434</v>
+        <v>-1.34097249333599</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-2.230922181111318</v>
+        <v>-2.047853040575568</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.4662579126756654</v>
+        <v>-0.1737515633224191</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.08833490255229</v>
+        <v>-0.8666955565185503</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.1955754714018028</v>
+        <v>-0.04688592362397515</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.8451133441511942</v>
+        <v>-0.6731145845845319</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>332</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1.272837723219403</v>
+        <v>1.061316746541586</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>1.931994261943984</v>
+        <v>1.561472994719068</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3.043246973574497</v>
+        <v>2.655830244499597</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1.667448020777307</v>
+        <v>1.297619047619044</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.2255440098502888</v>
+        <v>-0.3821062838090725</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.2217132202082723</v>
+        <v>0.1882982826289137</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.1642019583350063</v>
+        <v>-0.169976854215605</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.272343855709579</v>
+        <v>0.5546665758772491</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>1.114976157018127</v>
+        <v>1.410551109597591</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-1.542171554974381</v>
+        <v>-1.334030847194647</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>2.168789937367841</v>
+        <v>2.517597764166396</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.09473435478339809</v>
+        <v>0.3495862274488246</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>1.180607597855527</v>
+        <v>1.329297145633355</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.4008856675805887</v>
+        <v>-0.2288869080139264</v>
       </c>
     </row>
     <row r="30">
@@ -3465,306 +3465,306 @@
         <v>249</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.3190839694656518</v>
+        <v>0.0590581355873212</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.1247653462813361</v>
+        <v>-0.338348198580384</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.1316003872291134</v>
+        <v>-0.3368292698990416</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.5413873205881501</v>
+        <v>-0.9974590626764552</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-1.882889725089463</v>
+        <v>-2.672478954616523</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-2.790334972562817</v>
+        <v>-2.794950352793641</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-2.473438906126169</v>
+        <v>-2.460349525023055</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-2.137294698507283</v>
+        <v>-1.74041153441825</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-1.796670429327257</v>
+        <v>-1.382127226559</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-4.654621354171177</v>
+        <v>-4.373594931534839</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-1.244864681106066</v>
+        <v>-0.7865509105956363</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-3.218518657264788</v>
+        <v>-2.90687022900763</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-1.229030956361335</v>
+        <v>-1.080341408583507</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-2.609721008946046</v>
+        <v>-2.437722249379384</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.01779</t>
+          <t>X &gt; 0.01778</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>196</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2.110920704159525</v>
+        <v>1.761244959032616</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>2.030346855993649</v>
+        <v>1.685605562318969</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.4052408552919928</v>
+        <v>-0.7181826772520168</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.7453924515616634</v>
+        <v>0.4167264895908147</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.8133052647993253</v>
+        <v>-1.580060339803325</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-2.556747561694849</v>
+        <v>-2.312299946612534</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-1.110845676063065</v>
+        <v>-0.8654183473957886</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.04730207495185113</v>
+        <v>0.6787991434771499</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.6184883131072709</v>
+        <v>0.1393139715262848</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-2.99901935433509</v>
+        <v>-2.425542983482899</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.3677080588332871</v>
+        <v>0.6877549118000701</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-3.169342360239959</v>
+        <v>-3.045645739211714</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-1.548676887022765</v>
+        <v>-1.399987339244937</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-1.322941236796233</v>
+        <v>-1.15094247722957</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.01944</t>
+          <t>X &gt; 0.01943</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>160</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>1.89408396946564</v>
+        <v>1.864888175113009</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>2.157897876401819</v>
+        <v>2.156711089957163</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-1.36187350835322</v>
+        <v>-1.362026898357541</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-1.856648364764858</v>
+        <v>-1.857142857142861</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-4.269937917860553</v>
+        <v>-4.221391998094781</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-5.222563888225466</v>
+        <v>-5.198606479275853</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-2.182274247491634</v>
+        <v>-2.134262568501313</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-2.024342891278373</v>
+        <v>-1.975095328884656</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-1.460325047801149</v>
+        <v>-1.387067938021453</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-2.935243844131008</v>
+        <v>-2.835896518836435</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.610054997608799</v>
+        <v>0.7099630336274743</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-2.480566850035878</v>
+        <v>-2.356870229007633</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-1.025717703349287</v>
+        <v>-0.877028155571459</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-2.049982053122761</v>
+        <v>-1.877983293556099</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.02109</t>
+          <t>X &gt; 0.02108</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>129</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>4.883425054736968</v>
+        <v>4.854229260384336</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>4.822626558572367</v>
+        <v>4.821439772127711</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>2.102273778468486</v>
+        <v>2.102120388464165</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.09308247329199304</v>
+        <v>-0.09357696566999607</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-4.507341018635749</v>
+        <v>-4.458795098869977</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-5.76035458589989</v>
+        <v>-5.736397176950277</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-2.744289751367603</v>
+        <v>-2.696278072377282</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-3.986552193603949</v>
+        <v>-3.937304631210232</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-2.497146753227497</v>
+        <v>-2.423889643447801</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-4.122259348006978</v>
+        <v>-4.022912022712404</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.3242022844305055</v>
+        <v>0.4241103204491807</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-3.517388555462226</v>
+        <v>-3.393691934433981</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-1.611958013426808</v>
+        <v>-1.46326846564898</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-2.936609960099503</v>
+        <v>-2.76461120053284</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 0.02274</t>
+          <t>X &gt; 0.02273</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>106</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>4.122857554371308</v>
+        <v>4.093661760018676</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>5.341860140552761</v>
+        <v>5.340673354108105</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>2.11690007655244</v>
+        <v>2.116746686548119</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.5830634591044799</v>
+        <v>-0.5835579514824829</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-7.725126597105834</v>
+        <v>-7.676580677340063</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-7.427752567470748</v>
+        <v>-7.403795158521135</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-4.682274247491634</v>
+        <v>-4.634262568501313</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-7.979531570523655</v>
+        <v>-7.930284008129938</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-7.097117500631335</v>
+        <v>-7.023860390851638</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-7.947036296961194</v>
+        <v>-7.847688971666621</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-2.491360096730823</v>
+        <v>-2.391452060712147</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-7.173963076450974</v>
+        <v>-7.050266455422729</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-5.70732147693419</v>
+        <v>-5.558631929156363</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-6.424982053122754</v>
+        <v>-6.252983293556092</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.0244</t>
+          <t>X &gt; 0.02439</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>9.423845874227553</v>
+        <v>9.394650079874921</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>11.3840883525923</v>
+        <v>11.38290156614764</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>3.846459824980116</v>
+        <v>3.846306434975794</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>3.976684968568478</v>
+        <v>3.976190476190474</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-3.704461727384363</v>
+        <v>-3.655915807618591</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-2.216611507273079</v>
+        <v>-2.192654098323466</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-1.110845676063065</v>
+        <v>-1.062833997072744</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-3.958866700802183</v>
+        <v>-3.909619138408466</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-5.210325047801149</v>
+        <v>-5.137067938021453</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-7.250720034607198</v>
+        <v>-7.151372709312625</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.3125640500102449</v>
+        <v>-0.2126560139915696</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-3.849614469083491</v>
+        <v>-3.725917848055246</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-3.079289131920717</v>
+        <v>-2.93059958414289</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-2.853553481694185</v>
+        <v>-2.681554722127522</v>
       </c>
     </row>
   </sheetData>
@@ -3904,1093 +3904,1093 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.02352</t>
+          <t>X &lt; -0.02348</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-1.290439840058163</v>
+        <v>-1.319635634410794</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>3.050755019258958</v>
+        <v>3.049568232814302</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2.655983634503919</v>
+        <v>2.655830244499597</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-3.166172174288668</v>
+        <v>-3.166666666666671</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-2.513985536908166</v>
+        <v>-2.465439617142394</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.1643408736793006</v>
+        <v>0.1882982826289137</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.0796305144131324</v>
+        <v>0.1276421934034531</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1.993514251578766</v>
+        <v>2.042761813972483</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>5.503960666484559</v>
+        <v>5.577217776264256</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>7.034994251107086</v>
+        <v>7.13434157640166</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>9.211245473799281</v>
+        <v>9.311153509817956</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>6.864671245202217</v>
+        <v>6.988367866230462</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>7.634996582365005</v>
+        <v>7.783686130142833</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>5.479779851639151</v>
+        <v>5.651778611205813</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.02187</t>
+          <t>X &lt; -0.02183</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>1.155447605829288</v>
+        <v>1.543942229167072</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.4533524218563585</v>
+        <v>0.8616660449121198</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>3.69494467346496</v>
+        <v>4.071531660201018</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.1888061806896815</v>
+        <v>0.5978120978120955</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1.468698445775807</v>
+        <v>1.910364758661977</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1.766072475410894</v>
+        <v>2.183150277480905</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>1.681362116144726</v>
+        <v>2.122494188255445</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>6.66883892690344</v>
+        <v>7.062066833277505</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>5.698765861289765</v>
+        <v>6.124193323239801</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>7.576119792232625</v>
+        <v>8.003067445127527</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>9.189600452154252</v>
+        <v>9.600728799393252</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>7.405796786327755</v>
+        <v>7.857093734956329</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>6.985645933014347</v>
+        <v>7.461935808392504</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>7.211381583240879</v>
+        <v>7.710980670407871</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.02022</t>
+          <t>X &lt; -0.02018</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1.53368250961163</v>
+        <v>1.113076580910125</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.6524234238470754</v>
+        <v>0.2545371769136793</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1.71750605369057</v>
+        <v>2.03471223207724</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-1.071976831918143</v>
+        <v>-0.7339544513457525</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-1.610266385013837</v>
+        <v>-1.223203592297672</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-2.042819362678017</v>
+        <v>-1.675055754638173</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.06225129995362266</v>
+        <v>0.4382011996146318</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>5.434598714561048</v>
+        <v>5.769469888506656</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>5.373616558038272</v>
+        <v>5.732497279369859</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>5.253624769007679</v>
+        <v>5.633306379714284</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>6.508777625346028</v>
+        <v>6.878441294497044</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>5.813228770402084</v>
+        <v>6.211970350702508</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>4.663150909789401</v>
+        <v>5.09217474297926</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>4.158959552716667</v>
+        <v>4.61658192383522</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.01857</t>
+          <t>X &lt; -0.01853</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2.013465991937558</v>
+        <v>1.633534583952788</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.7213156067442483</v>
+        <v>-0.5021286890483623</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2.254699525354653</v>
+        <v>2.419050449708756</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.9858618479109253</v>
+        <v>-1.31846882399369</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-2.085949153815612</v>
+        <v>-2.360204152790914</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-2.350372876989503</v>
+        <v>-2.087418633971986</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.1878922250197235</v>
+        <v>0.06187002818377607</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>2.154027895238478</v>
+        <v>2.358468207026945</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>3.778438997142672</v>
+        <v>3.978954161426067</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>2.36672244800382</v>
+        <v>2.602639392765767</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>3.285616795361612</v>
+        <v>4.055957508765594</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>2.196399442098951</v>
+        <v>2.456665682594569</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>3.461641847212512</v>
+        <v>3.718966319566661</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>2.563781991821067</v>
+        <v>2.863038805891428</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.01691</t>
+          <t>X &lt; -0.01688</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>231</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2.064538514920187</v>
+        <v>2.035342720567556</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1.752053720557662</v>
+        <v>1.750866934113006</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>3.52178450030479</v>
+        <v>3.521631110300468</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.2440942522107434</v>
+        <v>-0.2445887445887465</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-1.648184671107309</v>
+        <v>-1.599638751341537</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.917910208571783</v>
+        <v>-0.8939527996221699</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.1368197020370943</v>
+        <v>-0.0888080230467736</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>1.127713385777909</v>
+        <v>1.176960948171626</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>3.664133826657732</v>
+        <v>3.737390936437428</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>1.515513731626569</v>
+        <v>1.614861056921143</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>2.60951387206768</v>
+        <v>2.709421908086355</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>1.3451907257217</v>
+        <v>1.468887346749945</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>2.223741171109594</v>
+        <v>2.372430718887422</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>1.150775522634824</v>
+        <v>1.322774282201486</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.01526</t>
+          <t>X &lt; -0.01523</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.4602604400538866</v>
+        <v>0.5843507158296291</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.4830612750946273</v>
+        <v>0.3041052267649818</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2.049074204065079</v>
+        <v>1.864764632587089</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.2185150339279502</v>
+        <v>0.04025127966495745</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.3197745191677441</v>
+        <v>-0.4489978612869621</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.3043968960882637</v>
+        <v>0.1495205565547693</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1.526876079305751</v>
+        <v>1.391796063420514</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1.71340220676084</v>
+        <v>1.577429101082771</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>4.593596520826303</v>
+        <v>4.472052583151189</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>2.763285567633702</v>
+        <v>2.671025305267804</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>3.538976566236251</v>
+        <v>3.444083554800116</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>2.592962561728832</v>
+        <v>2.525051595096606</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>2.826406479657251</v>
+        <v>2.78135946657838</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>1.744952587400128</v>
+        <v>1.727472732502541</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.01361</t>
+          <t>X &lt; -0.01358</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.3505902159980181</v>
+        <v>-0.5200620736432029</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.708643476981635</v>
+        <v>-0.6107018453662221</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.6509711031755998</v>
+        <v>0.7368536986573844</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.2213100189001977</v>
+        <v>-0.1282871357498294</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.5089730055798469</v>
+        <v>-0.3687800577962719</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.2115989759447601</v>
+        <v>-0.09599453897734378</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.9568234968692622</v>
+        <v>0.8383742474190825</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1.241634552330652</v>
+        <v>1.118810143752157</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>4.438797759216392</v>
+        <v>4.315668380386512</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>3.338252396470494</v>
+        <v>3.243083580666053</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>2.632298105378226</v>
+        <v>2.790186914224492</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>3.418555956981663</v>
+        <v>3.345866089400332</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>3.499658236500338</v>
+        <v>3.696976819552923</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>3.224140753894787</v>
+        <v>3.448509243757336</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.01196</t>
+          <t>X &lt; -0.01193</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>502</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.1087254037285916</v>
+        <v>0.07952960937596032</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.2903679959237309</v>
+        <v>0.2891812094790751</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.290018921925657</v>
+        <v>1.289865531921336</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.3725846197449414</v>
+        <v>-0.3730791121229444</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.6827513251673309</v>
+        <v>0.7312972449331028</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.378531729304413</v>
+        <v>1.402489138254026</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1.891430931791241</v>
+        <v>1.939442610781562</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>2.021971849757492</v>
+        <v>2.071219412151208</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>5.148240689250649</v>
+        <v>5.221497799030345</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>3.899915518418794</v>
+        <v>3.999262843713367</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>3.496011172907608</v>
+        <v>3.595919208926283</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>4.12799888701592</v>
+        <v>4.251695508044165</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>3.907051220953505</v>
+        <v>4.055740768731333</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>4.331990058431032</v>
+        <v>4.503988817997694</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.0103</t>
+          <t>X &lt; -0.01028</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.1588355222606808</v>
+        <v>0.04802770999673811</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.187400981991885</v>
+        <v>1.100509539569572</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.413747609659197</v>
+        <v>1.326926590014551</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.008822277808341994</v>
+        <v>-0.09357696566999607</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.626801212574229</v>
+        <v>1.58771652903701</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>2.545293254631673</v>
+        <v>2.480657086615622</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>3.547539417104645</v>
+        <v>3.505272315219621</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>2.304073257789952</v>
+        <v>2.264245756386664</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>5.34868116337897</v>
+        <v>5.328048341048309</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>4.49876236704911</v>
+        <v>4.504219760233326</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>3.983502202577746</v>
+        <v>3.990001793317404</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>5.104836876672195</v>
+        <v>5.133439848511742</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>4.684686023358786</v>
+        <v>4.738281921947916</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>4.755142170479729</v>
+        <v>4.832288024273367</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.008652</t>
+          <t>X &lt; -0.008626</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1.685750636132312</v>
+        <v>1.588248830850723</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.9584029269068708</v>
+        <v>0.8877955792383716</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.573732552252835</v>
+        <v>1.502884829259109</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.5675940594775639</v>
+        <v>0.6239416321383473</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.796981274058638</v>
+        <v>1.900140158273445</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>2.346880556218977</v>
+        <v>2.425132486676226</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>3.146008580791197</v>
+        <v>3.12109682620234</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>2.678939937004458</v>
+        <v>2.655264065818997</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>4.764422426946318</v>
+        <v>4.762049338145005</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>4.798342014454846</v>
+        <v>4.82094459087353</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>4.214852977406778</v>
+        <v>4.238493928961653</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>4.754281634812607</v>
+        <v>4.801074285494252</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>4.460393407761828</v>
+        <v>4.53201976372236</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>5.317442189301488</v>
+        <v>5.411581649697375</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.007</t>
+          <t>X &lt; -0.006975</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.427713411090018</v>
+        <v>1.336042021266863</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.8317557444221251</v>
+        <v>0.8205915357524987</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.14764425814424</v>
+        <v>1.237390528187539</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.7702551885346338</v>
+        <v>0.8606889564336271</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.957853960312043</v>
+        <v>1.891196654387493</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2.052182304667937</v>
+        <v>1.961347928018981</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>2.982700371797712</v>
+        <v>3.015180187324418</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>2.820200255929755</v>
+        <v>2.853298794722235</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>4.282060739000876</v>
+        <v>4.437400147084929</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>4.650416054346152</v>
+        <v>4.829377037394565</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>4.851806266644331</v>
+        <v>5.030505080233354</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>5.19075294691843</v>
+        <v>5.291306062785686</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>4.262987880407067</v>
+        <v>4.389562523253268</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>4.793292058552375</v>
+        <v>4.942558753049788</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.005347</t>
+          <t>X &lt; -0.005325</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1222</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.8742394522806975</v>
+        <v>0.9212607241326225</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.3268831464509248</v>
+        <v>0.3629662003414609</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.8322754278169953</v>
+        <v>0.8321220378126739</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.7988344502924321</v>
+        <v>0.798339957914429</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.078875502761377</v>
+        <v>1.127421422527149</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.9670842296141444</v>
+        <v>0.9910416385637575</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.864370597025548</v>
+        <v>1.912382276015869</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.970133377134069</v>
+        <v>2.019380939527785</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>3.136647128958266</v>
+        <v>3.209904238737963</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>3.759723422644768</v>
+        <v>3.859070747939342</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>3.636855324941045</v>
+        <v>3.736763360959721</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>3.753066537852824</v>
+        <v>3.876763158881069</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>3.414748745095885</v>
+        <v>3.563438292873712</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>3.885983576991812</v>
+        <v>4.057982336558474</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.003695</t>
+          <t>X &lt; -0.003674</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1450</v>
+        <v>1456</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.8937396168485634</v>
+        <v>0.919243456320153</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.04012928136049254</v>
+        <v>0.05907896916100697</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.3340631307652373</v>
+        <v>0.3893467280160934</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.3954177509376251</v>
+        <v>0.5192307692307736</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.6147039554176814</v>
+        <v>0.7854761337733507</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.5677253679728835</v>
+        <v>0.7148550591856875</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.722684430194313</v>
+        <v>1.890462706223957</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>2.219803114231269</v>
+        <v>2.386168407379074</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2.680784531799127</v>
+        <v>2.829965029011518</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>3.250100983455198</v>
+        <v>3.379762821822908</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>3.114365342436386</v>
+        <v>3.244303692968131</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>3.286674529274471</v>
+        <v>3.439833067695666</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>2.797558158719681</v>
+        <v>2.907312503769198</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>2.954328291704833</v>
+        <v>3.087676047103251</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.002042</t>
+          <t>X &lt; -0.002024</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1702</v>
+        <v>1706</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.8054689459914712</v>
+        <v>0.8271247090708584</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.4536044710160212</v>
+        <v>-0.3733123429660949</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.03190583436978045</v>
+        <v>0.02645493048185443</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.01392536007001866</v>
+        <v>-0.01951096968682009</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.2106958849563441</v>
+        <v>0.2532563020224501</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.2733281305538711</v>
+        <v>0.2915752323302385</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.479697583494278</v>
+        <v>1.520485379916039</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>2.068966967876555</v>
+        <v>2.168368914960595</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2.393902785434321</v>
+        <v>2.424479541462723</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>2.987934769264996</v>
+        <v>3.066067138842342</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>2.606970391263324</v>
+        <v>2.627460102795126</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.700102950199138</v>
+        <v>2.744243487287797</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.632478536368694</v>
+        <v>2.700785443490673</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2.505687747112262</v>
+        <v>2.598130422739338</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -0.00039</t>
+          <t>X &lt; -0.0003732</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1977</v>
+        <v>1981</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.1214083757314341</v>
+        <v>0.1612591428549521</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.085533149368771</v>
+        <v>-1.042355980138652</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.722345969192034</v>
+        <v>-0.7029703897803472</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.7437125385900245</v>
+        <v>-0.7478546188793516</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.170329529785775</v>
+        <v>-0.1265535326732774</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.2772000681142899</v>
+        <v>-0.2576044600936243</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.8508232765103827</v>
+        <v>0.9437283451786485</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.091182626659986</v>
+        <v>1.13412980993413</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.058633496182679</v>
+        <v>1.097157200797334</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.855790551417805</v>
+        <v>1.888674404939437</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.448762635443899</v>
+        <v>1.482615734283712</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.634885856084502</v>
+        <v>1.692221138988323</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.417061760484806</v>
+        <v>1.498981435544131</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.288725584712346</v>
+        <v>1.394669407100146</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.001262</t>
+          <t>X &lt; 0.001277</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2220</v>
+        <v>2224</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.2856156833657835</v>
+        <v>0.3412577305687918</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.100649132145186</v>
+        <v>-1.038482081651104</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.045577961794514</v>
+        <v>-1.00388083094181</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.4655102631004411</v>
+        <v>-0.4452723535457324</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.01414619496357261</v>
+        <v>0.05468713859586671</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.1216304649236193</v>
+        <v>-0.07720360157800599</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.8732813080639232</v>
+        <v>0.9412769998440069</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.8362556685776141</v>
+        <v>0.8801204984534721</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.8004808954676434</v>
+        <v>0.8431478893166755</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.192008408121247</v>
+        <v>1.23334808548011</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.7170369795907732</v>
+        <v>0.7594234652821541</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.111775492306471</v>
+        <v>1.177302432862867</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.871804819173235</v>
+        <v>0.9620006214069576</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.9624053342646377</v>
+        <v>1.076153397091396</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.002915</t>
+          <t>X &lt; 0.002928</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2492</v>
+        <v>2499</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.2773903895087173</v>
+        <v>-0.2528205743875773</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.287614944110999</v>
+        <v>-1.255559093895755</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.36187350835322</v>
+        <v>-1.308298389760978</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.7909432365597269</v>
+        <v>-0.7571428571428598</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.4478225332451657</v>
+        <v>-0.3663919980947838</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.5911536318152102</v>
+        <v>-0.5336064792758535</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.2055462653288842</v>
+        <v>0.2676982158124162</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.1211981908859556</v>
+        <v>0.1620095130521193</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.2026661310280389</v>
+        <v>0.2450849231230094</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.6184565168798173</v>
+        <v>0.6617525407874183</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.02748010066636652</v>
+        <v>0.01743602282314782</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.1899788963525637</v>
+        <v>0.2356667857982941</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.06965831330114014</v>
+        <v>0.0005728848447077439</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.1248215394790932</v>
+        <v>-0.0304942979578513</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.004567</t>
+          <t>X &lt; 0.004579</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2724</v>
+        <v>2731</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.1906998341254038</v>
+        <v>-0.1709305383372737</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.9957298260532923</v>
+        <v>-0.9671463140647703</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.9507797010978152</v>
+        <v>-0.9391117557094049</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.6373372617967448</v>
+        <v>-0.6066854842925125</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.4061141728990307</v>
+        <v>-0.3641380646882695</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.3652443572617443</v>
+        <v>-0.2910296125115792</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.2829144663229499</v>
+        <v>0.2906733524067775</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.05593570109699186</v>
+        <v>0.08115695965433645</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.2718898403543335</v>
+        <v>0.263884094201174</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.6528889511734661</v>
+        <v>0.6484041036461718</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.04476151615267554</v>
+        <v>-0.0683690791517293</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.1938090677321114</v>
+        <v>0.1728807779495227</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.03063325112941584</v>
+        <v>0.03403921901660567</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.1095260232355386</v>
+        <v>0.136617585242881</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.00622</t>
+          <t>X &lt; 0.006229</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2978</v>
+        <v>2987</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.2356077195423936</v>
+        <v>-0.1721024728495806</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.9084560109976465</v>
+        <v>-0.9025104269155406</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.632986108889412</v>
+        <v>-0.543176630977861</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.6368092226737048</v>
+        <v>-0.5624253713521483</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.6053936819356167</v>
+        <v>-0.4985659111382645</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.7101644244184939</v>
+        <v>-0.6425258503029454</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.2921938185372071</v>
+        <v>-0.1831246836284919</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.2717029315063328</v>
+        <v>-0.195508787204048</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.1801439612820346</v>
+        <v>-0.09856777062941546</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.2631375715013249</v>
+        <v>0.3497830928140502</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.2246765460153597</v>
+        <v>-0.1556630125727239</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.1714866217713649</v>
+        <v>-0.09749627520783122</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.2705968168482826</v>
+        <v>-0.2248269503488345</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.4142365863665347</v>
+        <v>-0.3105661526120045</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.007872</t>
+          <t>X &lt; 0.00788</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3212</v>
+        <v>3220</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.05092615648024434</v>
+        <v>0.07743078434759809</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.5972279390688158</v>
+        <v>-0.5904990774327956</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.5260160992199516</v>
+        <v>-0.4715230223885456</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.3336598590177289</v>
+        <v>-0.2938674228996874</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.5302283807372206</v>
+        <v>-0.4560724200618935</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.4813787375575629</v>
+        <v>-0.4457355916284271</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.03797477560595297</v>
+        <v>0.007153140905700184</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.1334414468198304</v>
+        <v>0.1483518760842841</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.05855900566481154</v>
+        <v>0.08032336632637538</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.251945210595359</v>
+        <v>0.2813395060082797</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.1218656866835772</v>
+        <v>-0.1091363452545124</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.02332238456275348</v>
+        <v>0.04219809397373098</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.1614553317339755</v>
+        <v>-0.135568528242267</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.1671987405449187</v>
+        <v>-0.1349708711958399</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.009525</t>
+          <t>X &lt; 0.00953</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3423</v>
+        <v>3434</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.1360281773447269</v>
+        <v>-0.08349165633133282</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.2033750627184858</v>
+        <v>-0.1688703053916782</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.2485979476191673</v>
+        <v>-0.1689111670402994</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.2057599289943965</v>
+        <v>-0.1395745034488485</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.2620707849934192</v>
+        <v>-0.1766218497095622</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.2693796853691524</v>
+        <v>-0.266272369846277</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.1341692912234151</v>
+        <v>-0.1364459746148512</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.114582451387129</v>
+        <v>0.08336419353817348</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.1280646838207886</v>
+        <v>0.1046327026308518</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.3447751228955482</v>
+        <v>0.3291442499463244</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.1061592464075503</v>
+        <v>-0.1370812296223818</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.003009792299891956</v>
+        <v>-0.02067337402801428</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.1670728435361966</v>
+        <v>-0.1828668276739691</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.07090668064247296</v>
+        <v>-0.07942476123227493</v>
       </c>
     </row>
     <row r="27">
@@ -5000,49 +5000,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3583</v>
+        <v>3594</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.06021486191999514</v>
+        <v>-0.02469110841933997</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.08542432727097093</v>
+        <v>-0.06551113226506544</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.2019541983921798</v>
+        <v>-0.1385967788799078</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.02878863751742955</v>
+        <v>0.006392440244574971</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.08835829594791278</v>
+        <v>0.1438776710739731</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.122569779276624</v>
+        <v>0.1260598166084677</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.08095695027995475</v>
+        <v>0.08061921174903119</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.2699939713574508</v>
+        <v>0.24214173288496</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.3638109611174656</v>
+        <v>0.3442898805650785</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.5608880209372913</v>
+        <v>0.5499549001952815</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.2883176858408092</v>
+        <v>0.2623419985690418</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.4221528152360889</v>
+        <v>0.4039811900240835</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.2131215823650052</v>
+        <v>0.2035923230039458</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.1198128115158141</v>
+        <v>0.09092321729532671</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3711</v>
+        <v>3722</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.2649611554336317</v>
+        <v>-0.24530346251764</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.004056887951648491</v>
+        <v>0.03539741703490762</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.2687112300082504</v>
+        <v>-0.2365576036404562</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.06420624421122056</v>
+        <v>0.09564684242795352</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.07818036170933595</v>
+        <v>0.1308014550847147</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.2021134443908252</v>
+        <v>0.2036345298492108</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.266623009097934</v>
+        <v>0.2650662905590906</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.298598997341486</v>
+        <v>0.2704739514590599</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.3601808725433102</v>
+        <v>0.3289540872269967</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.4404291033790813</v>
+        <v>0.4183675155444391</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.2240156868925922</v>
+        <v>0.1873670089162189</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.300540071590838</v>
+        <v>0.2723938053732411</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.1919547104438166</v>
+        <v>0.172696528822847</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.2713262195800255</v>
+        <v>0.2488974157399895</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3836</v>
+        <v>3847</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.1160511656694823</v>
+        <v>-0.098286098745902</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.06403559553164939</v>
+        <v>-0.03362613442675411</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.2108142413919438</v>
+        <v>-0.1798136134587409</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.06647675790058116</v>
+        <v>-0.03583478551037445</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.05954842804322169</v>
+        <v>0.1120711379384502</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.08505838024488099</v>
+        <v>0.08752050072934026</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.1446838581549912</v>
+        <v>0.1449582107194729</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.1083354012775857</v>
+        <v>0.08306912941620226</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.06173951871797811</v>
+        <v>0.03444973349621705</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.2939228225356629</v>
+        <v>0.2761097181697991</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.02634119931748558</v>
+        <v>-0.05796835930391353</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.1529662401152407</v>
+        <v>0.1301360079986011</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.06025441028115353</v>
+        <v>0.04682839328508948</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.1964986559491919</v>
+        <v>0.1806013178293995</v>
       </c>
     </row>
     <row r="30">
@@ -5156,309 +5156,309 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3919</v>
+        <v>3930</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.02606993539316704</v>
+        <v>-0.009477146034484463</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.09258370697928342</v>
+        <v>0.1220488248479725</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.04238857816077513</v>
+        <v>0.07228222026069631</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.1101370768233352</v>
+        <v>0.1398083623693296</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.1967117766404698</v>
+        <v>0.2489066041923849</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.2789321647411711</v>
+        <v>0.281502824232021</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.2846131697269101</v>
+        <v>0.2856458983179095</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.2646698475751279</v>
+        <v>0.2406981604337588</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.2687779083660331</v>
+        <v>0.2432424155781376</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.4526289572964757</v>
+        <v>0.4369666203139033</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.2368398012803965</v>
+        <v>0.2073873531390475</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.3621390923257621</v>
+        <v>0.3418705494202499</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.2370373986915268</v>
+        <v>0.2265396388828762</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.3241886536902001</v>
+        <v>0.3119022026271097</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.01779</t>
+          <t>X &lt; 0.01778</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3972</v>
+        <v>3983</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.1095233078241904</v>
+        <v>-0.09338254865357243</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.0007366617507926776</v>
+        <v>0.01492752282289445</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.06999317505125191</v>
+        <v>0.08576187638563226</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.03812812945914601</v>
+        <v>0.05388471177944609</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.1163657746790037</v>
+        <v>0.1548614488844109</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.2265567147896164</v>
+        <v>0.2157616250370893</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.1807566647978902</v>
+        <v>0.1688475393492013</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.1296917995210265</v>
+        <v>0.09308078752277282</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.1831876502124317</v>
+        <v>0.1452407194440397</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.3029352303156685</v>
+        <v>0.2749880482902896</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.1375707208792392</v>
+        <v>0.121035806525839</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.3119595717054438</v>
+        <v>0.3046730583198496</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.2332490723869327</v>
+        <v>0.224879474950626</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.221543626635551</v>
+        <v>0.211992855075593</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.01944</t>
+          <t>X &lt; 0.01943</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4008</v>
+        <v>4019</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.0810155082762023</v>
+        <v>-0.07955626933142668</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.01237548834211566</v>
+        <v>0.01239206242057378</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.1038206941847264</v>
+        <v>0.103543821245438</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.1480803559917305</v>
+        <v>0.1476970535049418</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.245714310170321</v>
+        <v>0.24298238124981</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.3078145978303155</v>
+        <v>0.3059564708110614</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.2118727014498347</v>
+        <v>0.2092545700977908</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.2069102228222803</v>
+        <v>0.2042524972022974</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.2095603247380993</v>
+        <v>0.2058744079029964</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.2707631349318049</v>
+        <v>0.2657999763164369</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.1299689841458189</v>
+        <v>0.1253658183117068</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.2532236736548938</v>
+        <v>0.2472705319970885</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.1963763350642864</v>
+        <v>0.1895141329857566</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.2366945935838274</v>
+        <v>0.2287285750679473</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.02109</t>
+          <t>X &lt; 0.02108</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4039</v>
+        <v>4050</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.1610739772273462</v>
+        <v>-0.1596318839566351</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.05606163976703016</v>
+        <v>-0.0558689198902016</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.01773770588408041</v>
+        <v>-0.01768437188623295</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.07654501631688504</v>
+        <v>0.07635467980294663</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.2186984457758143</v>
+        <v>0.2164313574115013</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.2825942536079893</v>
+        <v>0.2810017020942794</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.211447947268617</v>
+        <v>0.2092178357382721</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.2523876402420271</v>
+        <v>0.250003290444738</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.2298332113482005</v>
+        <v>0.2266805206715219</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.2840549438976794</v>
+        <v>0.2798533578285856</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.1427739486231516</v>
+        <v>0.1389353997760097</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.2653500022284163</v>
+        <v>0.2603558321967157</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.2057179402150666</v>
+        <v>0.2000207212490821</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.2474616210540219</v>
+        <v>0.2408438669377304</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 0.02274</t>
+          <t>X &lt; 0.02273</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4062</v>
+        <v>4073</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.1128178710251504</v>
+        <v>-0.1116781489202694</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.04202848589567765</v>
+        <v>-0.04188132130354916</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.006146771304365473</v>
+        <v>-0.006125820982418873</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.08834181205242686</v>
+        <v>0.08811798047653951</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.2757818070227671</v>
+        <v>0.2736471983775317</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.2918710012094223</v>
+        <v>0.2903974413318409</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.2452263669099324</v>
+        <v>0.2431884118908485</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.3324663515928208</v>
+        <v>0.3301571839861452</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.3343024417488891</v>
+        <v>0.331298908471922</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.3588412517863588</v>
+        <v>0.3550220487377587</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.2172198192570178</v>
+        <v>0.2137657814194327</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.3393150397279072</v>
+        <v>0.3348475624034037</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.3022726978321018</v>
+        <v>0.2971863756018323</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.3204635401810378</v>
+        <v>0.3146572662278473</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.0244</t>
+          <t>X &lt; 0.02439</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4084</v>
+        <v>4095</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.1987583541857987</v>
+        <v>-0.1975509680223269</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.1370239985981812</v>
+        <v>-0.1366295479780746</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.03021905169876504</v>
+        <v>-0.03013454570289298</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.008822277808341994</v>
+        <v>-0.008787193318262609</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.1502612025890002</v>
+        <v>0.1487347075582406</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.1433940785389467</v>
+        <v>0.14245493919843</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.1453962487195639</v>
+        <v>0.1438944280857228</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.2051803361054922</v>
+        <v>0.2034891627027662</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.2555590314358369</v>
+        <v>0.2531759644175793</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.2998344337554855</v>
+        <v>0.2967272918490949</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.1578590103320678</v>
+        <v>0.1551192073707597</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.2305197872622102</v>
+        <v>0.2270326267404741</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.215867363970176</v>
+        <v>0.211839031928541</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.2106692691103476</v>
+        <v>0.2061131655403656</v>
       </c>
     </row>
   </sheetData>
